--- a/Excel/7_RiceCultivation_WIP_v01.xlsx
+++ b/Excel/7_RiceCultivation_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E68F83C-8596-4A0B-B891-A3CDF1A59BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E701DC-2B92-4BA7-9D96-DD372C51324D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="255" yWindow="420" windowWidth="38085" windowHeight="20460" activeTab="1" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" firstSheet="3" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -20,8 +20,11 @@
     <sheet name="Input - Rice" sheetId="70" r:id="rId5"/>
     <sheet name="7.1.1-2 Rice cultivation" sheetId="69" r:id="rId6"/>
     <sheet name="Constants - Rice cultivation" sheetId="110" r:id="rId7"/>
-    <sheet name="Constants - Common" sheetId="111" r:id="rId8"/>
+    <sheet name="Constants - Common" sheetId="119" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
     <definedName name="AgResidues_Equations_Leaching.VEERG_6_3_1_1__1__LeachingAndRunoffEmissionsCropAndPastureResidue">_xlfn.LAMBDA(_xlpm.Mleachcp,_xlpm.EFleach,_xlpm.CgN2O, _xlpm.Mleachcp * _xlpm.EFleach * _xlpm.CgN2O * 10 ^ (-3))</definedName>
     <definedName name="AgResidues_Equations_Leaching.VEERG_6_3_1_1__1__LeachingAndRunoffEmissionsCropAndPastureResidue_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Mleachcp","mass of nitrogen lost through leaching and runoff from the crop residue c or pasture residue p (kg N)";"EFleach","emission factor for leaching and runoff (kg N2O-N/kg N)";"CgN2O","factor to convert elemental mass of nitrous oxide to molecular mass (dimensionless)";"c","Crop residue type";"p","Pasture residue type"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -207,9 +210,12 @@
     <definedName name="CommonLivestock_InputFunctions.AverageLiveweightEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.Livestock_LookupMCFState">_xlfn.LAMBDA(_xlpm.MMS,_xlpm.MMSArray,_xlpm.State,_xlpm.StateArray,_xlpm.ReturnArray, _xlfn.XLOOKUP(_xlpm.MMS, _xlpm.MMSArray, _xlfn.XLOOKUP(_xlpm.State, _xlpm.StateArray, _xlpm.ReturnArray)))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR([0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain" localSheetId="7">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_GetMovementLiveweightGain">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate, _xlfn.LET(_xlpm.ym, TEXT(_xlpm.MovementDate, "yyyymm"), IFERROR(INDEX(_xlfn._xlws.FILTER(#REF!, (TEXT(#REF!, "yyyymm") = _xlpm.ym) * (#REF! = _xlpm.LivestockClass)), 1), "")))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth">_xlfn.LAMBDA(_xlpm.HeadAtStart,_xlpm.Month,_xlpm.LivestockClass, _xlpm.HeadAtStart + [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStartOfMonth, MAX(_xlpm.HeadAtStartOfMonth - [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadLostDuringMonth(_xlpm.Month, _xlpm.LivestockClass), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_LiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.LivestockClass,_xlpm.MovementDate,_xlpm.WeightAtMovementDate,_xlpm.Head, IFERROR(_xlpm.Head * (_xlpm.WeightAtMovementDate + [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownDuringMonthPerHead(_xlpm.LivestockClass, _xlpm.MovementDate)), 0))</definedName>
@@ -221,12 +227,29 @@
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionalAverageLiveweightRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart,_xlpm.LiveweightAtStart,_xlpm.LiveweightGain, [0]!CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) * CommonLivestock_InputFunctions.LivestockMovement_AverageLiveweightRemainingHead(_xlpm.Month, _xlpm.LiveweightAtStart, _xlpm.LiveweightGain))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAddedDuringMonth(_xlpm.Month, _xlpm.LivestockClass) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_ProportionHeadRemainingAtEndOfMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, IFERROR(MIN(1, [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadRemainingAtMonthEnd(_xlpm.Month, _xlpm.LivestockClass, _xlpm.HeadAtStart) / [0]!CommonLivestock_InputFunctions.LivestockMovement_HeadAtEndOfMonth(_xlpm.HeadAtStart, _xlpm.Month, _xlpm.LivestockClass)), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightAddedDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
+    <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth" localSheetId="7">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass, IFERROR(SUM(_xlfn._xlws.FILTER(#REF!, (#REF! &gt;= EOMONTH(_xlpm.Month, -1) + 1) * (#REF! &lt;= EOMONTH(_xlpm.Month, 0)) * (#REF! = _xlpm.LivestockClass))), 0))</definedName>
     <definedName name="CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonthAddedAndRemaining">_xlfn.LAMBDA(_xlpm.Month,_xlpm.LivestockClass,_xlpm.HeadAtStart, [0]!CommonLivestock_InputFunctions.LivestockMovement_LiveweightGrownFromMonthStartTotal(_xlpm.LivestockClass, _xlpm.Month, _xlpm.HeadAtStart) + [0]!CommonLivestock_InputFunctions.LivestockMovement_TotalLiveweightGrownDuringMonth(_xlpm.Month, _xlpm.LivestockClass))</definedName>
+    <definedName name="CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data">_xlfn.LAMBDA(_xlfn.MAKEARRAY(19, 3, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Symbol","Manure management system","";"1","Anaerobic lagoon","Anaerobic lagoon (m=1)";"2","Liquid systems","Liquid systems (m=2)";"3","Daily spread","Daily spread (m=3)";"3a","Sump and dispersal system","Sump and dispersal system (m=3a)";"3b","Drains to paddock","Drains to paddock (m=3b)";"4","Solid storage","Solid storage (m=4)";"5","Drylot (feed pad)","Drylot (feed pad) (m=5)";"6","Composting (passive windrow)","Composting (passive windrow) (m=6)";"7","Digester / covered lagoons","Digester / covered lagoons (m=7)";"8","Deep litter","Deep litter (m=8)";"9","Pit storage","Pit storage (m=9)";"10","Poultry manure with bedding","Poultry manure with bedding (m=10)";"11","Poultry manure without bedding","Poultry manure without bedding (m=11)";"11a","Belt manure removal","Belt manure removal (m=11a)";"11b","Manure stored in house","Manure stored in house (m=11b)";"12","Direct processing","Direct processing (m=12)";"13","Direct application","Direct application (m=13)";"14","Pasture range and paddock","Pasture range and paddock (m=14)"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="Fertiliser_Equations_Lime.VEERG_5_3_1_1__1_LimeApplication">_xlfn.LAMBDA(_xlpm.Mlime,_xlpm.FracLime,_xlpm.Plime,_xlpm.EFlime,_xlpm.FracDol,_xlpm.Pdol,_xlpm.EFdol,_xlpm.CgCO2, ((_xlpm.Mlime * _xlpm.FracLime * _xlpm.Plime * _xlpm.EFlime) + (_xlpm.Mlime * _xlpm.FracDol * _xlpm.Pdol * _xlpm.EFdol)) * _xlpm.CgCO2 * 10 ^ -3)</definedName>
     <definedName name="Fertiliser_Equations_Organic.VEERG_5_2_1_1__2_MassOfNitrogenInOrganicFertiliser">_xlfn.LAMBDA(_xlpm.Morganicjf,_xlpm.FNorganicf, _xlpm.Morganicjf * _xlpm.FNorganicf)</definedName>
     <definedName name="getOverlappingReportingCycles">_xlfn.LAMBDA(_xlpm.ProductionCycleStart,_xlpm.ProductionCycleEnd,_xlpm.ReportingStartMonth,_xlpm.ReportingStartDay, _xlfn.LET(_xlpm.S, _xlpm.ProductionCycleStart, _xlpm.E, _xlpm.ProductionCycleEnd, _xlpm.m, _xlpm.ReportingStartMonth, _xlpm.d, _xlpm.ReportingStartDay, _xlpm.A, _xlpm.S - 364, _xlpm.ya, YEAR(_xlpm.A), _xlpm.yb, YEAR(_xlpm.E), _xlpm.firstYear, _xlpm.ya + (DATE(_xlpm.ya, _xlpm.m, _xlpm.d) &lt; _xlpm.A), _xlpm.lastYear, _xlpm.yb - (DATE(_xlpm.yb, _xlpm.m, _xlpm.d) &gt; _xlpm.E), MAX(0, _xlpm.lastYear - _xlpm.firstYear + 1)))</definedName>
+    <definedName name="Inoput_Cell_Livestock_antibiotics">#REF!</definedName>
+    <definedName name="Inoput_Cell_Livestockantibiotics">#REF!</definedName>
+    <definedName name="Input_Cell_CO2_for_carbonation">#REF!</definedName>
+    <definedName name="Input_Cell_CO2forcarbonation">#REF!</definedName>
+    <definedName name="Input_Cell_Livestock_antibiotics">#REF!</definedName>
+    <definedName name="Input_Cell_Livestock_tags">#REF!</definedName>
+    <definedName name="Input_Cell_LivestockAntibiotics">#REF!</definedName>
+    <definedName name="Input_Cell_Nylon_netting_for_horticulture">#REF!</definedName>
+    <definedName name="Input_Cell_Nylonnettingforhorticulture">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets__Plastic">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets__Wood">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets_Plastic">#REF!</definedName>
+    <definedName name="Input_Cell_Pallets_Wood">#REF!</definedName>
+    <definedName name="Range_LivestockStartingValues">#REF!</definedName>
     <definedName name="RiceCultivation_Equations.VEERG_7_1_1_1__1_MethaneEmissionsFromRiceCultivation">_xlfn.LAMBDA(_xlpm.A_ricewpo,_xlpm.EF_ricewpo,_xlpm.t_ricewpo, SUM(_xlpm.A_ricewpo * _xlpm.EF_ricewpo * _xlpm.t_ricewpo) * 10 ^ -3)</definedName>
     <definedName name="RiceCultivation_Equations.VEERG_7_1_1_1__1_MethaneEmissionsFromRiceCultivation_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(4, 4, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"A_ricewpo","annual area of rice cultivation under water regime w, pre-season water regime p, and organic amendment condition o","ha","Input";"EF_ricewpo","emission factor for rice cultivation under conditions w, p, and o","kg CH4/ha/day","Calculated from 7.1.1.1, (2)";"t_ricewpo","cultivation period for rice under conditions w, p, and o","days","Input";"s","number of cropping seasons in reporting period managed this way","seasons","Input"}, _xlpm.r, _xlpm.c))))</definedName>
     <definedName name="RiceCultivation_Equations.VEERG_7_1_1_1__1_MethaneEmissionsFromRiceCultivation_LatexEquation">_xlfn.LAMBDA("E_{rice}=\sum_w\sum_p\sum_o(A_{rice,wpo}\times EF_{rice,wpo}\times t_{rice,wpo})\times 10^{-3}")</definedName>
@@ -279,6 +302,9 @@
     <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Unit">_xlfn.LAMBDA("fraction")</definedName>
     <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Variable">_xlfn.LAMBDA("SFp")</definedName>
     <definedName name="RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Variation">_xlfn.LAMBDA("")</definedName>
+    <definedName name="Step1">#REF!</definedName>
+    <definedName name="Step2">#REF!</definedName>
+    <definedName name="Step3">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1902,7 +1928,7 @@
     </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="40" fillId="4" borderId="0" xfId="8">
       <alignment horizontal="left" vertical="center"/>
@@ -2240,9 +2266,6 @@
     <xf numFmtId="0" fontId="45" fillId="13" borderId="0" xfId="41" applyBorder="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="8" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="70">
     <cellStyle name="Alert" xfId="62" xr:uid="{34EFE908-8095-4010-8F93-8CFE88055637}"/>
@@ -2317,126 +2340,6 @@
     <cellStyle name="Variable type other" xfId="66" xr:uid="{6646F6F7-E4F9-4165-8015-E25083532B5B}"/>
   </cellStyles>
   <dxfs count="66">
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3298,6 +3201,126 @@
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4445,6 +4468,7 @@
               <a:latin typeface="Times New Roman"/>
               <a:cs typeface="Times New Roman"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>7.1.1-2 Rice cultivation CH4 emissions</a:t>
           </a:fld>
           <a:endParaRPr lang="en-AU" sz="1400" b="0">
@@ -4526,6 +4550,7 @@
               <a:latin typeface="Times New Roman"/>
               <a:cs typeface="Times New Roman"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>Emission factor for rice cultivation</a:t>
           </a:fld>
           <a:endParaRPr lang="en-AU" sz="1000">
@@ -4607,6 +4632,7 @@
               <a:latin typeface="Times New Roman"/>
               <a:cs typeface="Times New Roman"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>Methane emissions from rice cultivation</a:t>
           </a:fld>
           <a:endParaRPr lang="en-AU" sz="1000" b="1">
@@ -4744,6 +4770,7 @@
               <a:latin typeface="Times New Roman"/>
               <a:cs typeface="Times New Roman"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>Organic amendments scaling factor</a:t>
           </a:fld>
           <a:endParaRPr lang="en-AU" sz="1000">
@@ -5244,8 +5271,8 @@
       <xdr:rowOff>4762</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2984215" cy="485839"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="TextBox 7">
@@ -5483,7 +5510,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="8" name="TextBox 7">
@@ -5557,8 +5584,8 @@
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2169055" cy="182294"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -5600,6 +5627,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -5805,7 +5833,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -5869,8 +5897,8 @@
       <xdr:rowOff>109537</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="9164111" cy="226922"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -6534,7 +6562,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="TextBox 3">
@@ -6599,8 +6627,8 @@
       <xdr:rowOff>185737</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3657411" cy="429348"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="TextBox 5">
@@ -6642,6 +6670,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -6924,7 +6953,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="TextBox 5">
@@ -6981,6 +7010,26 @@
     <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Home"/>
+      <sheetName val="Constants - Common"/>
+      <sheetName val="Acknowledgements"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7061,7 +7110,7 @@
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{FE260FFD-8165-44FA-8171-CF7DA9E6EDC2}" name="Amendment mix name"/>
     <tableColumn id="2" xr3:uid="{1656D970-5568-46C3-8CF9-6544B58E60EE}" name="Straw added &lt; 30 days before cultivation (t/ha)"/>
-    <tableColumn id="8" xr3:uid="{6AB8226E-B5ED-4236-BF1D-312497BC4C8F}" name="Straw added 30+ days before cultivation (t/ha)" dataDxfId="13" dataCellStyle="Content normal"/>
+    <tableColumn id="8" xr3:uid="{6AB8226E-B5ED-4236-BF1D-312497BC4C8F}" name="Straw added 30+ days before cultivation (t/ha)" dataDxfId="53" dataCellStyle="Content normal"/>
     <tableColumn id="3" xr3:uid="{7414D722-C23C-43BF-8BE4-9A787F770773}" name="Compost (t/ha)"/>
     <tableColumn id="4" xr3:uid="{10821F0A-FFAB-47C5-A2D8-0C77A91D1E11}" name="Farm yard manure (t/ha)"/>
     <tableColumn id="5" xr3:uid="{7554AF1F-8437-4EC1-A35B-D5ADAFFC9535}" name="Green manure (t/ha)"/>
@@ -7072,12 +7121,12 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{A98080EA-F2FB-4179-A336-59EF5AF50E8F}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6C986F30-D9EC-4803-8DA0-95980EFC62A0}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{8E44BE92-8969-4CB0-B814-3C00C2C18F3C}" name="SA 4 Name">
+    <tableColumn id="1" xr3:uid="{DB52865D-6F2D-4651-9C10-87FA05E28EDB}" name="SA 4 Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7086,16 +7135,16 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{3B270221-00F4-4B48-BE2F-1F9DCAB7874A}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CE5A8FF1-51D1-4DC7-A67C-E1BB1D169339}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D82C5D5A-F88F-46E7-868F-025402490369}" name="Gas">
+    <tableColumn id="1" xr3:uid="{DE7AB944-8934-40CD-9BD0-1EB0965AAF53}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6DC661F8-0615-4FB7-8AE2-83962657C55A}" name="CO2-e factor">
+    <tableColumn id="2" xr3:uid="{BF74DAA5-1727-4598-8BDF-A1FFEAF36797}" name="CO2-e factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7104,7 +7153,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="25" xr:uid="{79E591EE-C4BF-4FA2-8F75-39DA84C25602}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{84EB336F-AD27-4469-81D9-D75BF392704A}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7113,19 +7162,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{BABC03E3-165B-407A-BF04-28738E72D28A}" name="Gas">
+    <tableColumn id="1" xr3:uid="{6FF8E719-A496-4146-95F1-5C74FB0907DF}" name="Gas">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{CF0196FE-D2CF-4F66-8847-9CE3DB549E9B}" name="Conversion factor">
+    <tableColumn id="5" xr3:uid="{141A87B3-BDC7-4BC9-86AA-9AEF8E4516F0}" name="Conversion factor">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{71C50FB6-28B8-4C5F-B7F7-F9E98423215B}" name="Conversion factor 1">
+    <tableColumn id="2" xr3:uid="{6EEA02FE-9CA9-42CC-9715-CE1AE379A798}" name="Conversion factor 1">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{9E60D175-C714-4272-922B-6384C81A6A4A}" name="Conversion factor 2">
+    <tableColumn id="3" xr3:uid="{63DBA7EA-762D-4502-893E-4F59C65F1D06}" name="Conversion factor 2">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{77C6E5B1-2CB1-4714-9B60-3FC1F2C784D3}" name="Conversion factor combined">
+    <tableColumn id="4" xr3:uid="{D45503ED-E349-402E-BE70-522640844EB2}" name="Conversion factor combined">
       <calculatedColumnFormula>Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 1]]/Table_GasToMolecularConversionFactor[[#This Row],[Conversion factor 2]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7134,7 +7183,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{5EB24DAD-7938-4A28-8102-A92DD6232701}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{B64F6EE9-601E-431C-889B-F490F94AAF6D}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7154,52 +7203,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{7C646E3D-156E-438B-9E75-102B5E96E255}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{E3EAE8D7-79F7-4CFF-AA60-81BEB0D1F996}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3F6652C3-1BDE-4F33-9D5E-1BA7F24CFE1E}" name="MAT" totalsRowDxfId="53" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{90558006-D3B7-45CA-BB08-CBC5FB2D525E}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{68D3A033-0C56-472E-A3CF-B482905871CF}" name="MAP" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{31536C54-9D90-4BA1-8630-5A5825932E3D}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{18D7CFC5-1F89-47C0-AF12-0FD6A80AD2C8}" name="Frost days per year" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{C736DFB1-216D-41C0-9BDA-AF1DACA0D28E}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{694DED4D-19CA-49A7-A7A4-ED3CD36E0BA2}" name="Elevation" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{EBC9733B-D9D6-44EF-92E6-EAE63368707E}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{BE47AD00-59A1-4916-A3FF-4E905492D142}" name="MAP:PET" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{86BD24B4-BCF5-43E4-9791-66486A239A29}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{8CD0BB0E-B9A0-4065-920B-F859089361EB}" name="Min temp" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{04625927-EE66-47A4-9B56-E9FF16A40381}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{9AD474F5-6F0E-4F15-87EA-A3E86BD8CD84}" name="Max temp" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{0B6D7849-AF37-4F92-B3BC-F00F938473A4}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{4132B96D-08DF-47B8-9134-F88DA6CBA26A}" name="Min rainfall" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{79B2D447-365C-4E5B-9B46-EB9A6FEABC8F}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{799D2CC4-68A8-4F6B-B5E8-BA9B134CD629}" name="Max rainfall" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{15AE00CB-0DCC-4C76-9A69-811B2102ABD0}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{FF3C7CFE-CC8F-4407-9CD2-DB7BCF735828}" name="Min frost days" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{453B192C-DCF9-4759-9B4F-A3C3978C4EAF}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{9CB12B6D-F283-41CE-A0AC-7DA70F3FEA35}" name="Max frost days" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{399D591D-E030-4FE8-8A4D-14B154F55401}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{DE6B8D57-DEA5-4CDB-BEA5-6794B3B8B4C1}" name="Min elevation" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{7BB2477B-60BA-4ACB-81E8-FD8FE87495FF}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F1C5507D-FFFD-4456-AAE0-9309987F0339}" name="Max elevation" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{0A47AD04-56FF-4DD7-A870-3813EAA5B320}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{BB91B1DF-4B57-426B-BF6A-71715747D3B2}" name="Min MAP:PET" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{FE9A6C0E-201D-4A67-8D4D-C6A488CA05EA}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{7674CAA3-6E67-48AA-BF62-AECA84F01CB9}" name="Max MAP:PET" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{3378CC43-2399-435F-A3FE-BB19D039E80F}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7208,16 +7257,16 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="42" xr:uid="{3FAC77B2-7BB0-4B78-B387-3E2D5CA67215}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{0D035090-ADB1-4F10-9C19-A48DE1D5960D}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{9DF69629-1C76-40A4-BBA1-FB28BF754268}" name="Climate zone" totalsRowCellStyle="Content bold">
+    <tableColumn id="1" xr3:uid="{1ECE3957-9413-4408-BDB8-77552A7231E8}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{99A9C0E3-7924-426C-A581-5C219452362E}" name="Wet or Dry Zone" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{03FFA737-2FA7-48E9-A115-73FA50C9393D}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7226,7 +7275,7 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="43" xr:uid="{AE4202F8-BB52-48CE-B368-8D0A44A67525}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BEF50EEC-58C1-4511-A309-1BA0389F0DBD}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7234,16 +7283,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{4BD1B715-E9FF-4B2E-A162-3DD06FA33AAE}" name="Temperature Zone">
+    <tableColumn id="1" xr3:uid="{FCB9DB5A-F79A-4195-A2D3-345C295DFC8A}" name="Temperature Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3FDEC609-65F3-40EC-B489-B99CC8E44680}" name="MAT">
+    <tableColumn id="2" xr3:uid="{25D74762-0A2D-4400-B824-894D618905BB}" name="MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{25C140A7-4F53-46DB-A6E5-3FFA5FE81DD6}" name="Min MAT">
+    <tableColumn id="3" xr3:uid="{1205EC90-4A04-43FC-A053-69E387CE1D3F}" name="Min MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C2D4126F-3B56-4A19-AD7E-FA0C2ECA0D87}" name="Max MAT">
+    <tableColumn id="4" xr3:uid="{A0CC6FD8-F8F6-4A79-9CDF-BE796852DAF1}" name="Max MAT">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7252,7 +7301,7 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="44" xr:uid="{F8066D7D-5B7A-4C2D-96C5-0B642AEDBDD8}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{356F1A3E-799D-40CF-8D17-7ECCC24A8932}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7260,16 +7309,16 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{CFC2CD32-0D6A-477F-9AB9-8CC735000875}" name="Rainfall Zone">
+    <tableColumn id="1" xr3:uid="{F2FCA308-B091-442E-94CA-E0A51124F1E1}" name="Rainfall Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{66F05498-A494-40EC-A370-E31F9319F6E9}" name="Annual rainfall">
+    <tableColumn id="2" xr3:uid="{71D5D2C7-753E-4961-91F7-5D8FD4EBBBB8}" name="Annual rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{0FEB24E7-52AA-4E09-8CAD-E3593BA1850C}" name="Min rainfall">
+    <tableColumn id="3" xr3:uid="{6FA6F6A2-93E0-4091-A742-AE671B909E65}" name="Min rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B9588CB4-A6E3-43EF-86F2-28512F6C0466}" name="Max rainfall">
+    <tableColumn id="4" xr3:uid="{EBBE1093-D022-42FA-A758-FE815C9D665B}" name="Max rainfall">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7278,16 +7327,16 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="45" xr:uid="{371EB3B0-E5DE-49F4-9F8F-370B9594177E}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{C2C58793-EC57-49E4-811D-88A2C42FD549}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1EC0469C-3AAC-4C25-8B45-E899791ECD1F}" name="Leaching Zone">
+    <tableColumn id="1" xr3:uid="{8DEDD535-7F20-4744-95AD-A4D8DE59C041}" name="Leaching Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D8738CB7-C0A6-466E-AD54-75590BF18BAC}" name="Leaching criteria">
+    <tableColumn id="2" xr3:uid="{413AA76F-C255-42F1-A6D5-5CD24BBBAF26}" name="Leaching criteria">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7296,16 +7345,16 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="46" xr:uid="{8320C659-C167-4CAA-9C06-854A612436E9}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{99111242-9C75-4E29-97AB-7B805B522700}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{2CBE0C09-88F8-4FC0-91F9-37AD76A1AEAA}" name="Data source">
+    <tableColumn id="1" xr3:uid="{BDB9D991-F5EB-4B03-9F51-46A4472289C1}" name="Data source">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{390BA082-D34B-4509-BBAD-72ABE42C4B39}" name="Data score">
+    <tableColumn id="2" xr3:uid="{01E97336-A13E-4773-A06E-95DCCDC3855D}" name="Data score">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7314,16 +7363,16 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="47" xr:uid="{D7EAD11A-DC1E-416A-A0F3-2127BEE727A4}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{2F5DAA02-E4E8-4624-A2C5-096D1B60A921}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D0B2F492-E516-47ED-A029-67FEF667A678}" name="Is in leaching zone">
+    <tableColumn id="1" xr3:uid="{1FF542F2-F612-45D7-AC03-2F170C811D2C}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{51E6CA6F-68DC-47AB-A1BB-C75D3CA8FA3B}" name="FracWET" dataDxfId="37">
+    <tableColumn id="2" xr3:uid="{CAF3234F-1744-4CC7-97FB-29E26283D105}" name="FracWET" dataDxfId="19">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7344,7 +7393,7 @@
   </autoFilter>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{6CF21226-E2F8-4356-887C-701D50A69505}" name="Regime name"/>
-    <tableColumn id="7" xr3:uid="{03F35653-B2DB-4AB6-99EC-0912FB20CD21}" name="Area under cultivation (hectares)" dataDxfId="12" dataCellStyle="Content normal"/>
+    <tableColumn id="7" xr3:uid="{03F35653-B2DB-4AB6-99EC-0912FB20CD21}" name="Area under cultivation (hectares)" dataDxfId="52" dataCellStyle="Content normal"/>
     <tableColumn id="2" xr3:uid="{EA5A5A10-60BF-4C8A-8D3B-469871BE7F8E}" name="Pre-cultivation water regime (select)" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{85A41168-485F-4954-954D-E24F2E46EB1B}" name="Water regime (select)" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{EF7FE10B-862C-4478-9622-5C7E7DA42BCC}" name="Water regime sub-type (select)" dataCellStyle="Input select"/>
@@ -7356,7 +7405,7 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="48" xr:uid="{BE2E746E-A542-4963-9138-4CB3534F691E}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{7C4B023C-39DC-4A61-B287-ACF14E1CC6BC}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7365,19 +7414,19 @@
     <filterColumn colId="4" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{10155645-FDE5-446A-BDDD-C71CD77DD825}" name="Production system j">
+    <tableColumn id="1" xr3:uid="{08E69A42-D0D6-4FBD-91D3-EC4843CB8995}" name="Production system j">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A33C56B8-DAE9-434B-8228-CD6E219067F7}" name="EFN2O">
+    <tableColumn id="2" xr3:uid="{FB6F1229-41A4-4698-ADAF-85A7F3BDC850}" name="EFN2O">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{415F2F98-1C0C-4F1B-A357-E4F0898F9DA1}" name="Production system only">
+    <tableColumn id="3" xr3:uid="{48F26286-FAFA-4819-9AFA-F6ECAE3F6B49}" name="Production system only">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{364F973B-700F-4051-9AE8-A5B5A5144B24}" name="Irrigation method">
+    <tableColumn id="4" xr3:uid="{99A2A834-E5E1-4659-9E7A-BC2543C1E44F}" name="Irrigation method">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6B401083-C682-49B6-9293-290F6E0CCE9C}" name="Rainfall zone">
+    <tableColumn id="5" xr3:uid="{4316727C-0C8D-4A2E-947B-24A6E48379FF}" name="Rainfall zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7386,16 +7435,16 @@
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="49" xr:uid="{F2CB8BB6-7664-477A-B6EF-EAA92A00C8A0}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="26" xr:uid="{8771BEDC-DFB7-49CC-BFDB-089589025B03}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{0CAEDF1E-5A86-4C59-ADB4-2A63E7ABD4DD}" name="Irrigation type i">
+    <tableColumn id="1" xr3:uid="{0349773D-F8B1-4F20-8D67-02CFFC1D5B01}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{57851871-7E08-4269-B67C-A96E5A947487}" name="FracWET" dataDxfId="36" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{E1A81332-451C-4F13-819A-08B47B324E1A}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7404,16 +7453,16 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="50" xr:uid="{BFE0DDAE-EACA-4433-A3E7-753CE50EADFD}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{0B56AF9D-3A20-46F2-9DF6-908E16C583F9}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{04E57D99-757F-4374-BB84-42339A5C3083}" name="Climate zone">
+    <tableColumn id="1" xr3:uid="{19ECEEA9-A0E2-448E-9242-5EB4612E5A30}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{92543612-DE1F-4C45-B1F2-46B34452C302}" name="EFPRP" dataDxfId="35" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{D5BC812F-1B20-433B-A220-45B290E585E4}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7422,16 +7471,16 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="51" xr:uid="{31E1F417-A09B-41DA-9456-3458FDF04264}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="28" xr:uid="{9254172A-1F0A-4DA8-AF3D-FBD2D01D814B}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
   <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5C54F0C5-3505-4964-A85B-6C95900D28A5}" name="Month">
+    <tableColumn id="1" xr3:uid="{622EF0B5-08C2-435D-AD90-194AA40AF483}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{DE5E22FE-C43A-4172-9EDB-6FE00B1DF854}" name="Season" dataDxfId="34" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1B155342-2AE7-4ACF-A9BA-20CE30CBC6E1}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7440,7 +7489,7 @@
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="52" xr:uid="{AF70AA04-1AD5-4DF8-9CC4-5F92B5EE2A0A}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{187B9ADF-B9E3-4BCF-ABE8-F47F94E4CCD2}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7460,52 +7509,52 @@
     <filterColumn colId="15" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{FD606263-AC8F-4B13-96E2-C9CA0ECFC2B3}" name="Temperature zone">
+    <tableColumn id="1" xr3:uid="{3E609039-97C4-4729-BC48-B95334FF569D}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{328E4735-CE75-4070-9C88-AE6AC281FA52}" name="MAT (ºC)" dataDxfId="33" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{E18B5A5E-83DE-4F01-B188-8A16EF097844}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{AAAA9F18-86A5-4F62-9B13-8EC468FD3268}" name="Anaerobic lagoon" dataDxfId="32" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{D36388A3-2885-4653-8CA5-464AC2653131}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{16CDDAC7-40E8-4B7E-A5A7-534574EF9960}" name="Digester / covered lagoons" dataDxfId="31" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{9C1AA35B-D1B9-4F13-9AFE-E084527288D4}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{7BE7531C-242C-4F06-B612-2455D4071B48}" name="Liquid systems" dataDxfId="30" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{36AFD6DE-B5F7-4FA0-8661-5137CBBDF314}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4AA6EA91-67D5-4225-8E66-D79949E45C79}" name="Daily spread" dataDxfId="29" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{5C9AC720-CEA6-4B40-B794-DA1221D8A639}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{A682CC91-6B5E-45D1-857C-0228079BCC7C}" name="Composting (passive windrow)" dataDxfId="28" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{454AD809-4295-4C51-9928-79A9335C5131}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{516A42DC-F452-4685-9EE1-8DB5323E888F}" name="Solid storage" dataDxfId="27" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{3B58D073-0610-4780-89E8-72FD5F9DE29F}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{3E59565B-237D-4BF7-8514-8C00EE69787F}" name="Pit storage" dataDxfId="26" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{4054B9BB-77F9-4163-856D-1F02090BD29E}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B94C989A-1174-49BC-8E63-5C88C372C925}" name="Deep litter" dataDxfId="25" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{7761C4A1-7DEB-4A74-ABFE-16C4A40CA65E}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{4E416B5A-6B9A-4444-8C96-0603C11DC870}" name="Poultry manure with bedding" dataDxfId="24" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{8CBEF1D1-4341-4566-AE85-0BAE80513B23}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{2302252A-7FB0-4046-9B12-B1CD2F1BBED4}" name="Poultry manure without bedding" dataDxfId="23" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{8AC3B56F-0E3B-46E4-881E-4A4C23336DB8}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{50CED419-50AF-49B3-8F42-E496D5B781AB}" name="Direct processing" dataDxfId="22" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{5E2D555B-CCCB-47A0-ABC6-4BBE59B69EB8}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{FACDE6F8-8A2F-4040-8D12-2E35D0831482}" name="Direct application" dataDxfId="21" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{1ABF9296-D829-4357-B8D0-BF198B1CB558}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{2134A83A-1EB7-471E-ADAA-05ADE14C7593}" name="Pasture range and paddock" dataDxfId="20" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{143C946F-C17F-411D-99BA-FB5337573E30}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{1C3199CA-00F6-4D2D-9A1A-14E5576B6B3A}" name="MAT raw" dataDxfId="19" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{6876FAEC-5772-4EAC-8F56-60AF713901CD}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7514,16 +7563,16 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{1F061C8D-6288-498A-A3C6-A58C7CA98367}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
-  <autoFilter ref="D257:E259" xr:uid="{1F061C8D-6288-498A-A3C6-A58C7CA98367}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{462A48A5-6B2F-4D2D-8025-572DAB9FE02B}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
+  <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{6441941C-5801-414B-9EFC-BFCD02E9AABA}" name="Climate Zone">
+    <tableColumn id="1" xr3:uid="{9C964A67-F781-4D99-8B91-5BFC8B5214FC}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{AFFF76A7-AEC2-426D-9FB9-7DCEAE399701}" name="EFNi &amp; EFN2Oi" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{EC008960-0F7E-4D6F-90B0-1B33D47696C5}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7542,10 +7591,10 @@
     <tableColumn id="1" xr3:uid="{3A2980B6-3A2D-485C-8340-4AB52CBFBB99}" name="Water regime type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorGrowingSeason_Data(),Table_SourceData_WaterScalingFactorGrowingSeason[[#Headers],[Water regime type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{49BAF191-8DE2-478B-90F3-B9943FCEA9BA}" name="Water regime sub-type" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{49BAF191-8DE2-478B-90F3-B9943FCEA9BA}" name="Water regime sub-type" dataDxfId="51" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorGrowingSeason_Data(),Table_SourceData_WaterScalingFactorGrowingSeason[[#Headers],[Water regime type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5202109C-BFD9-4463-9F2B-0B19C4500C07}" name="SFw" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{5202109C-BFD9-4463-9F2B-0B19C4500C07}" name="SFw" dataDxfId="50" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorGrowingSeason_Data(),Table_SourceData_WaterScalingFactorGrowingSeason[[#Headers],[Water regime type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7563,7 +7612,7 @@
     <tableColumn id="1" xr3:uid="{FF0717D8-C262-491B-A316-62679EA1B7D7}" name="Water regime prior to cultivation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Data(),Table_SourceData_WaterScalingFactorPreSeason[[#Headers],[Water regime prior to cultivation]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3527B004-E130-4F0F-B6D1-0D475D57A7A4}" name="SFp" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{3527B004-E130-4F0F-B6D1-0D475D57A7A4}" name="SFp" dataDxfId="49" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Data(),Table_SourceData_WaterScalingFactorPreSeason[[#Headers],[Water regime prior to cultivation]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7581,7 +7630,7 @@
     <tableColumn id="1" xr3:uid="{4FCCD68A-6FAE-4D17-88E1-28AE833F5E5E}" name="Organic amendment i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Data(),Table15[[#Headers],[Organic amendment i]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1F56CED6-01B8-4B36-AC56-E8A59F878F68}" name="CFOAi" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1F56CED6-01B8-4B36-AC56-E8A59F878F68}" name="CFOAi" dataDxfId="48" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Data(),Table15[[#Headers],[Organic amendment i]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7632,20 +7681,20 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3AE6144E-A1E7-4518-B032-EF188F35C422}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1C2292D7-9159-4DA8-868F-97A60010C689}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{A67EF497-7B1B-4776-9D83-A8AD1BEAF517}" name="State/Territory">
+    <tableColumn id="1" xr3:uid="{556CCF88-C654-4845-97D7-9D7D362BCE69}" name="State/Territory">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{6E9614A8-2F7E-4491-9C0D-E14664D3CBD5}" name="Common Name">
+    <tableColumn id="2" xr3:uid="{281E9821-9727-41EE-9BB2-A0EE34626517}" name="Common Name">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{48FCC7EC-93CF-4022-930C-DFF884BE9C3A}" name="Abbreviation">
+    <tableColumn id="3" xr3:uid="{DB9ED2A9-4530-4389-9F51-62F4D51CBA86}" name="Abbreviation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10179,25 +10228,25 @@
         <f>HYPERLINK("#'Constants - Rice cultivation'!A1", "Constants - Rice cultivation")</f>
         <v>Constants - Rice cultivation</v>
       </c>
-      <c r="D15" s="123" t="s">
+      <c r="D15" s="35" t="s">
         <v>153</v>
       </c>
-      <c r="E15" s="123">
+      <c r="E15" s="35">
         <v>2</v>
       </c>
-      <c r="F15" s="123">
+      <c r="F15" s="35">
         <v>0</v>
       </c>
-      <c r="G15" s="123">
+      <c r="G15" s="35">
         <v>2</v>
       </c>
-      <c r="H15" s="123">
+      <c r="H15" s="35">
         <v>0</v>
       </c>
-      <c r="I15" s="123">
+      <c r="I15" s="35">
         <v>2</v>
       </c>
-      <c r="J15" s="123">
+      <c r="J15" s="35">
         <v>0</v>
       </c>
     </row>
@@ -10206,25 +10255,25 @@
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
-      <c r="D16" s="123" t="s">
+      <c r="D16" s="35" t="s">
         <v>154</v>
       </c>
-      <c r="E16" s="123">
+      <c r="E16" s="35">
         <v>0</v>
       </c>
-      <c r="F16" s="123">
+      <c r="F16" s="35">
         <v>2</v>
       </c>
-      <c r="G16" s="123">
+      <c r="G16" s="35">
         <v>0</v>
       </c>
-      <c r="H16" s="123">
+      <c r="H16" s="35">
         <v>2</v>
       </c>
-      <c r="I16" s="123">
+      <c r="I16" s="35">
         <v>0</v>
       </c>
-      <c r="J16" s="123">
+      <c r="J16" s="35">
         <v>2</v>
       </c>
     </row>
@@ -10262,10 +10311,10 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D22" s="123" t="s">
+      <c r="D22" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="E22" s="123">
+      <c r="E22" s="35">
         <v>100</v>
       </c>
       <c r="F22" s="37" t="s">
@@ -10280,15 +10329,15 @@
       <c r="I22" s="37" t="s">
         <v>153</v>
       </c>
-      <c r="J22" s="123">
+      <c r="J22" s="35">
         <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D23" s="123" t="s">
+      <c r="D23" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="E23" s="123">
+      <c r="E23" s="35">
         <v>100</v>
       </c>
       <c r="F23" s="37" t="s">
@@ -10303,7 +10352,7 @@
       <c r="I23" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="J23" s="123">
+      <c r="J23" s="35">
         <v>100</v>
       </c>
     </row>
@@ -10497,63 +10546,63 @@
       <c r="D363" s="91"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J211 E212:I212">
-    <cfRule type="cellIs" dxfId="11" priority="79" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F86">
-    <cfRule type="cellIs" dxfId="10" priority="62" operator="lessThan">
+    <cfRule type="cellIs" dxfId="47" priority="62" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F128:F129">
-    <cfRule type="cellIs" dxfId="9" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="46" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F140:F141">
-    <cfRule type="cellIs" dxfId="8" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="45" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F152:F153">
-    <cfRule type="cellIs" dxfId="7" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="44" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F164:F165">
-    <cfRule type="cellIs" dxfId="6" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="43" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F252:F253">
-    <cfRule type="cellIs" dxfId="5" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="42" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F257:F258">
-    <cfRule type="cellIs" dxfId="4" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="41" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F262:F263">
-    <cfRule type="cellIs" dxfId="3" priority="91" operator="lessThan">
+    <cfRule type="cellIs" dxfId="40" priority="91" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F286:F287">
-    <cfRule type="cellIs" dxfId="2" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="39" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F291:F292">
-    <cfRule type="cellIs" dxfId="1" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="38" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F296:F297">
-    <cfRule type="cellIs" dxfId="0" priority="83" operator="lessThan">
+    <cfRule type="cellIs" dxfId="37" priority="83" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J211 E212:I212">
+    <cfRule type="cellIs" dxfId="36" priority="79" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12138,22 +12187,22 @@
         <f>HYPERLINK("#'Input - Rice'!A1", "Rice")</f>
         <v>Rice</v>
       </c>
-      <c r="D9" s="123" t="s">
+      <c r="D9" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="E9" s="123" t="s">
+      <c r="E9" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="F9" s="123" t="s">
+      <c r="F9" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="H9" s="123" t="s">
+      <c r="H9" s="35" t="s">
         <v>147</v>
       </c>
-      <c r="J9" s="123" t="s">
+      <c r="J9" s="35" t="s">
         <v>147</v>
       </c>
-      <c r="L9" s="123" t="s">
+      <c r="L9" s="35" t="s">
         <v>147</v>
       </c>
       <c r="AG9" s="1"/>
@@ -12161,27 +12210,27 @@
       <c r="AI9" s="1"/>
     </row>
     <row r="10" spans="1:35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D10" s="123" t="str" cm="1">
+      <c r="D10" s="35" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorGrowingSeason_Data(),Table_SourceData_WaterScalingFactorGrowingSeason[[#Headers],[Water regime type]],0)</f>
         <v>Upland</v>
       </c>
-      <c r="E10" s="123" t="str" cm="1">
+      <c r="E10" s="35" t="str" cm="1">
         <f t="array" ref="E10">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorGrowingSeason_Data(),Table_SourceData_WaterScalingFactorGrowingSeason[[#Headers],[Water regime type]],0)</f>
         <v>Paddy rotation</v>
       </c>
-      <c r="F10" s="123" cm="1">
+      <c r="F10" s="35" cm="1">
         <f t="array" ref="F10">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorGrowingSeason_Data(),Table_SourceData_WaterScalingFactorGrowingSeason[[#Headers],[Water regime type]],0)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="123" t="str">
+      <c r="H10" s="35" t="str">
         <f>E10</f>
         <v>Paddy rotation</v>
       </c>
-      <c r="J10" s="123" t="str">
+      <c r="J10" s="35" t="str">
         <f>E12</f>
         <v>Continuously flooded</v>
       </c>
-      <c r="L10" s="123" t="str">
+      <c r="L10" s="35" t="str">
         <f>E15</f>
         <v>Regular rainfed</v>
       </c>
@@ -12205,15 +12254,15 @@
         <f t="array" ref="F11">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorGrowingSeason_Data(),Table_SourceData_WaterScalingFactorGrowingSeason[[#Headers],[Water regime type]],0)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="123" t="str">
+      <c r="H11" s="35" t="str">
         <f>E11</f>
         <v>Fallow without flooding in previous year</v>
       </c>
-      <c r="J11" s="123" t="str">
+      <c r="J11" s="35" t="str">
         <f>E13</f>
         <v>Single drainage period</v>
       </c>
-      <c r="L11" s="123" t="str">
+      <c r="L11" s="35" t="str">
         <f>E16</f>
         <v>Drought prone</v>
       </c>
@@ -12235,11 +12284,11 @@
         <f t="array" ref="F12">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorGrowingSeason_Data(),Table_SourceData_WaterScalingFactorGrowingSeason[[#Headers],[Water regime type]],0)</f>
         <v>1</v>
       </c>
-      <c r="J12" s="123" t="str">
+      <c r="J12" s="35" t="str">
         <f>E14</f>
         <v>Multiple drainage periods</v>
       </c>
-      <c r="L12" s="123" t="str">
+      <c r="L12" s="35" t="str">
         <f>E17</f>
         <v>Deep water</v>
       </c>
@@ -12354,19 +12403,19 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="123" t="s">
+      <c r="D24" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="E24" s="123" t="s">
+      <c r="E24" s="35" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="123" t="str" cm="1">
+      <c r="D25" s="35" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Data(),Table_SourceData_WaterScalingFactorPreSeason[[#Headers],[Water regime prior to cultivation]], 0)</f>
         <v>Non flooded pre-season &lt;180 days</v>
       </c>
-      <c r="E25" s="123" cm="1">
+      <c r="E25" s="35" cm="1">
         <f t="array" ref="E25">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Data(),Table_SourceData_WaterScalingFactorPreSeason[[#Headers],[Water regime prior to cultivation]], 0)</f>
         <v>1</v>
       </c>
@@ -12444,19 +12493,19 @@
       </c>
     </row>
     <row r="38" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D38" s="123" t="s">
+      <c r="D38" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="E38" s="123" t="s">
+      <c r="E38" s="35" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="39" spans="4:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="123" t="str" cm="1">
+      <c r="D39" s="35" t="str" cm="1">
         <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Data(),Table15[[#Headers],[Organic amendment i]],0)</f>
         <v>Straw incorporated shortly (&lt;30 days) before cultivation</v>
       </c>
-      <c r="E39" s="123" cm="1">
+      <c r="E39" s="35" cm="1">
         <f t="array" ref="E39">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Data(),Table15[[#Headers],[Organic amendment i]],0)</f>
         <v>1</v>
       </c>
@@ -12671,7 +12720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C96C07E-3BBC-40AD-9550-B73B24462357}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE7628F-C552-4DBE-BEDA-1D3AB479C827}">
   <dimension ref="A1:BY259"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -14075,31 +14124,31 @@
       </c>
       <c r="T97" s="35"/>
     </row>
-    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D98" s="49" t="str" cm="1">
-        <f t="array" ref="D98:D101">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
+    <row r="98" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D99" s="49" t="str" cm="1">
+        <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
-      </c>
-    </row>
-    <row r="99" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D99" s="49" t="str">
-        <v>MAT = mean annual temperature</v>
       </c>
     </row>
     <row r="100" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D100" s="49" t="str">
-        <v>MAP = mean annual precipitation</v>
+        <v>MAT = mean annual temperature</v>
       </c>
     </row>
     <row r="101" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D101" s="49" t="str">
+        <v>MAP = mean annual precipitation</v>
+      </c>
+    </row>
+    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D102" s="49" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="102" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D102" s="49"/>
-    </row>
-    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D103" s="49"/>
+    </row>
     <row r="104" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="105" spans="4:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D105" s="6" t="str" cm="1">
@@ -16663,12 +16712,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16867,24 +16918,25 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgACcARgByAHkAJwAgAHQAbwAgACcARAByAHkAJwAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAG8AcgAgAEQAcgB5ACAAWgBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIAB3AGUAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGgAaQBnAGgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAAaQBuACAATQBBAFQAIAB2AGEAbAB1AGUAIABmAG8AcgAgAHcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGMAaABhAG4AZwBlAGQAIAAxADAAIAB0AG8AIAAxADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAbQBpAG4AIABhAG4AZAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAATQBBAFQALAAgAE0AQQBQACwAIABmAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByACwAIABlAGwAZQB2AGEAdABpAG8AbgAsACAATQBBAFAAOgBQAEUAVAAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQBzACAAZgByAG8AbQAgAHIAZQBhAGwAIABjAGwAaQBtAGEAdABlACAAZABhAHQAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEEARgAgAGEAYwBjAGUAcAB0AHMAIAByAGEAaQBuAGYAYQBsAGwAIABhAHMAIABhACAAcAByAG8AeAB5ACAAZgBvAHIAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADEANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAXAAiACwAIABcACIATQBBAFAAXAAiACwAIABcACIARgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgBcACIALAAgAFwAIgBFAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAAdABlAG0AcABcACIALAAgAFwAIgBNAGEAeAAgAHQAZQBtAHAAXAAiACwAIABcACIATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBhAHgAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIATQBpAG4AIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AYQB4ACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AYQB4ACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAG4AdABhAG4AZQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAPgAgADEAOAAgAEMAXAAiACwAIABcACIAPgAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgA+ACAAMQAwADAAMAAgAG0AbQAgAC0AIABkIiAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADEAMAAwADAALgAwADAAMQAsACAAMgAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAD4AIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAD4AIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAD4AIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgA+ACAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgA+ACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAD4AIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAPgCjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGQAbwBlAHMAIABuAG8AdAAgAG8AYwBjAHUAcgBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAZCKjAygANdg43DXYR9wwACkAKwA12GDcNdhc3DXYVtw12FncIAA12GTcNdhO3DXYYdw12FLcNdhf3CAADiE12FzcNdhZ3DXYUdw12FbcNdhb3DXYVNwgADXYUNw12E7cNdhd3DXYTtw12FDcNdhW3DXYYdw12GbcXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHMAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAGUAcwAgAC0AIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIAAtACAAbgBvAHQAIABpAG4AIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlAFwAIgAsACAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABkAGEAdABhACAAcwBjAG8AcgBlAHMAIABmAG8AcgAgAHMAYwBvAHAAZQAgADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAWABYAFgAWABYAFgAWABYAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAYQB0AGEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBEAGEAdABhACAAcwBjAG8AcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AdABlAHIAbgBhAHQAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG8AcgAgAHIAZQBnAGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAaQBuAHQAZQBuAHMAaQB0AHkAIABjAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgAGEAcABwAHIAbwB2AGUAZAAgAG0AZQB0AGgAbwBkAFwAIgAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGUAcgBpAGYAaQBlAGQAIABjAHIAZQBkAGUAbgB0AGkAYQBsACAAbQBhAHQAYwBoAGkAbgBnACAASQBTAE8AMQA0ADAANgA3AFwAIgAsACAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAJwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAJwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAJwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5ACcALAAgACcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAnACAAYQBuAGQAIAAnAGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZAAnACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAJwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIAAnAEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuACcAXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMgA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYAUABSAFAAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAbwByACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYAUABSAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQwBoAGEAbgBnAGUAZAAgACcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIAAnAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAJwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgADwAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgACcAUABvAHUAbAB0AHIAeQAgAHcAaQB0AGgAIABhAG4AZAAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAnACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIAAnAE0AQQBUACAAcgBhAHcAJwAgAGMAbwBsAHUAbQBuACAAdABvACAAYQBsAGwAbwB3ACAAbABvAG8AawB1AHAAIABvAGYAIABuAHUAbQBiAGUAcgBzAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBOAGkAIAAmACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAJgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA8AHQAPgA8AHMAPgBcACIAIAAmAFwAbgAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAUwBVAEIAUwBUAEkAVABVAFQARQAoAEMAZQBsAGwALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMQAsAFwAIgBcACIAKQAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAyACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEQAZQBsAGkAbQBpAHQAZQByACwAXAAiADwALwBzAD4APABzAD4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgACYAXABuACAAIAAgACAAIAAgACAAIABcACIAPAAvAHMAPgA8AC8AdAA+AFwAIgAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC8ALwBzAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAYQB2AGcAVABlAG0AcAAsAGEAdgBnAFIAYQBpAG4ALABmAHIAbwBzAHQARABhAHkAcwAsAGUAbABlAHYALABtAGEAcABfAHAAZQB0ACwAXABuACAAIAAgACAAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkALABtAGEAeABUAGUAbQBwAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARgByAG8AcwB0AEEAcgByAGEAeQAsAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBQAEUAVABBAHIAcgBhAHkALABtAGEAeABQAEUAVABBAHIAcgBhAHkALABcAG4AIAAgACAAIABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAG0AYQBzAGsALABcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AVABlAG0AcABBAHIAcgBhAHkAKQA8AD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPAA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAPgA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAPAA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAD4APQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQApADwAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAPgA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQA8AD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFAARQBUAEEAcgByAGEAeQApAD4APQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQA8AD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAPgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAEkAdABlAG0AQQByAHIAYQB5ACwAIABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAPAAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQA+ACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgAnAHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQA8AFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuACcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAPgBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAJgAgAFwAIgAgAHQAbwAgAFwAIgAgACYAIABlAG4AZABzAFQAZQB4AHQAIAAmACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABUAEUAWABUAEIARQBGAE8AUgBFACgARgBPAFIATQBVAEwAQQBUAEUAWABUACgARgB1AG4AYwB0AGkAbwBuACkALAAgAFwAIgAoAFwAIgApACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQAsACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQAsAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAD0AXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAIAA9ACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkAPQBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQA9AEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAEEAcgByAGEAeQA9AFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAPgAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwAnAFwAIgAgACYAIABzAGgAIAAmACAAXAAiACcAIQBcACIAIAAmACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAE0ASQBOACgAVABlAG0AcABlAHIAYQB0AHUAcgBlAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBBAFgAKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATQBNAFMALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZQBtAHAAbABvAHkAZQBkACAAZAB1AHIAaQBuAGcAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABzAGUAYQBzAG8AbgAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAdwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADMALgAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBXAGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHMAdQBiACAALQAgAHQAeQBwAGUAXAAiACwAIABcACIAUwBGAHcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFUAcABsAGEAbgBkAFwAIgAsACAAXAAiAFAAYQBkAGQAeQAgAHIAbwB0AGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVQBwAGwAYQBuAGQAXAAiACwAIABcACIARgBhAGwAbABvAHcAIAB3AGkAdABoAG8AdQB0ACAAZgBsAG8AbwBkAGkAbgBnACAAaQBuACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwBsAHkAIABmAGwAbwBvAGQAZQBkAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAgAHAAZQByAGkAbwBkAFwAIgAsACAAMAAuADcAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBNAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUAIABwAGUAcgBpAG8AZABzAFwAIgAsACAAMAAuADUANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAFIAZQBnAHUAbABhAHIAIAByAGEAaQBuAGYAZQBkAFwAIgAsACAAMAAuADUANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAEQAcgBvAHUAZwBoAHQAIABwAHIAbwBuAGUAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAYQBpAG4AZgBlAGQAIABhAG4AZAAgAGQAZQBlAHAAIAB3AGEAdABlAHIAXAAiACwAIABcACIARABlAGUAcAAgAHcAYQB0AGUAcgBcACIALAAgADAALgAwADYAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGIAYQBzAGUAZAAgAG8AbgAgAHQAaABlACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABlAG0AcABsAG8AeQBlAGQAIABpAG4AIAB0AGgAZQAgAHAAcgBlACAALQAgAHMAZQBhAHMAbwBuACAAYgBlAGYAbwByAGUAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABwAGUAcgBpAG8AZABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAcAByAGkAbwByACAAdABvACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAcABlAHIAaQBvAGQAIABwAFwAIgAsACAAXAAiAFMARgBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAgAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAPAAxADgAMAAgAGQAYQB5AHMAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuACAAZgBsAG8AbwBkAGUAZAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAA+ADEAOAAwACAAZABhAHkAcwBcACIALAAgADAALgA4ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBsAG8AbwBkAGUAZAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAA+ADMAMAAgAGQAYQB5AHMAXAAiACwAIAAyAC4ANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AZgBsAG8AbwBkAGUAZAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAA+ADMANgA1ACAAZABhAHkAcwBcACIALAAgADAALgA1ADkAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBGAE8AQQBpAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADMALgAzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AYwBsAHUAZABlAGQAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGEAcwAgAHAAZQByACAAVgBFAEUAUgBHACAAZQBxAHUAYQB0AGkAbwBuACAAZABlAHMAYwByAGkAcAB0AGkAbwBuADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAaABlAHIAZQAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGkAcwAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIAB0AGgAZQAgAHIAaQBjAGUAIABmAGkAZQBsAGQAcwAgAHIAYQB0AGgAZQByACAAdABoAGEAbgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACwAIABTAEYAXwBvACAAaQBzACAAcwBlAHQAIAB0AG8AIAAxAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAaQBcACIALAAgAFwAIgBDAEYATwBBAGkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdAByAGEAdwAgAGkAbgBjAG8AcgBwAG8AcgBhAHQAZQBkACAAcwBoAG8AcgB0AGwAeQAgACgAPAAzADAAIABkAGEAeQBzACkAIABiAGUAZgBvAHIAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgBcACIALAAgADEALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AHIAYQB3ACAAaQBuAGMAbwByAHAAbwByAGEAdABlAGQAIABsAG8AbgBnACAAKAA+ADMAMAAgAGQAYQB5AHMAKQAgAGIAZQBmAG8AcgBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgAsACAAMAAuADEAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbQBwAG8AcwB0AFwAIgAsACAAMAAuADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGEAcgBtACAAeQBhAHIAZAAgAG0AYQBuAHUAcgBlAFwAIgAsACAAMAAuADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAHIAZQBlAG4AIABtAGEAbgB1AHIAZQBcACIALAAgADAALgA0ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAYwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0ACAALwAgAGgAYQAgAC8AIABkAGEAeQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA3AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxAC4AMQA5ACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADcALgAxADoAIABSAGkAYwBlACAAQwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA3AC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAFIAaQBjAGUAIABDAHUAbAB0AGkAdgBhAHQAaQBvAG4AIABDAEgANAAgAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuAEUAXwByAGkAYwBlAFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AHIAaQBjAGUAfQA9AFwAXABzAHUAbQBfAHcAXABcAHMAdQBtAF8AcABcAFwAcwB1AG0AXwBvACgAQQBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAHQAXwB7AHIAaQBjAGUALAB3AHAAbwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXABuAEEAXwByAGkAYwBlAHcAcABvACAAPQAgAGEAbgBuAHUAYQBsACAAYQByAGUAYQAgAG8AZgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIAB1AG4AZABlAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHcALAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHAALAAgAGEAbgBkACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAYwBvAG4AZABpAHQAaQBvAG4AIABvACAAKABoAGEAKQBcAG4ARQBGAF8AcgBpAGMAZQB3AHAAbwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHUAbgBkAGUAcgAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAIAB3ACwAIABwACwAIABhAG4AZAAgAG8AIAAoAGsAZwAgAEMASAA0AC8AaABhAC8AZABhAHkAKQBcAG4AdABfAHIAaQBjAGUAdwBwAG8AIAA9ACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAcABlAHIAaQBvAGQAIABmAG8AcgAgAHIAaQBjAGUAIAB1AG4AZABlAHIAIABjAG8AbgBkAGkAdABpAG8AbgBzACAAdwAsACAAcAAsACAAYQBuAGQAIABvACAAKABkAGEAeQBzACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAF8AcgBpAGMAZQB3AHAAbwAsACAARQBGAF8AcgBpAGMAZQB3AHAAbwAsACAAdABfAHIAaQBjAGUAdwBwAG8ALABcAG4AIAAgACAAIABTAFUATQAoAEEAXwByAGkAYwBlAHcAcABvACAAKgAgAEUARgBfAHIAaQBjAGUAdwBwAG8AIAAqACAAdABfAHIAaQBjAGUAdwBwAG8AKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwByAGkAYwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsAcgBpAGMAZQB9AD0AXABcAHMAdQBtAF8AdwBcAFwAcwB1AG0AXwBwAFwAXABzAHUAbQBfAG8AKABBAF8AewByAGkAYwBlACwAdwBwAG8AfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewByAGkAYwBlACwAdwBwAG8AfQBcAFwAdABpAG0AZQBzACAAdABfAHsAcgBpAGMAZQAsAHcAcABvAH0AKQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAF8AcgBpAGMAZQB3AHAAbwBcACIALAAgAFwAIgBhAG4AbgB1AGEAbAAgAGEAcgBlAGEAIABvAGYAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIAB3ACwAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABwACwAIABhAG4AZAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGMAbwBuAGQAaQB0AGkAbwBuACAAbwBcACIALAAgAFwAIgBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwByAGkAYwBlAHcAcABvAFwAIgAsACAAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5AFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANwAuADEALgAxAC4AMQAsACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHQAXwByAGkAYwBlAHcAcABvAFwAIgAsACAAXAAiAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkACAAZgBvAHIAIAByAGkAYwBlACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwBcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcwBcACIALAAgAFwAIgBuAHUAbQBiAGUAcgAgAG8AZgAgAGMAcgBvAHAAcABpAG4AZwAgAHMAZQBhAHMAbwBuAHMAIABpAG4AIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAbQBhAG4AYQBnAGUAZAAgAHQAaABpAHMAIAB3AGEAeQBcACIALAAgAFwAIgBzAGUAYQBzAG8AbgBzAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBkAGQAZQBkACAAJwBuAHUAbQBiAGUAcgAgAG8AZgAgAHMAZQBhAHMAbwBuAHMAJwAgAHYAYQByAGkAYQBiAGwAZQAgAGEAcwAgAHAAZQByACAAVgBFAEUAUgBHACAAZABlAHMAYwByAGkAcAB0AGkAbwBuACAAaQBuACAANwAuADIALgAxACAAJwBXAGgAZQByAGUAIAB0AGgAZQByAGUAIABpAHMAIABtAG8AcgBlACAAdABoAGEAbgAgAG8AbgBlACAAYwByAG8AcABwAGkAbgBnACAAcwBlAGEAcwBvAG4AIABwAGUAcgAgAHkAZQBhAHIALAAgAEEAcgBpAGMAZQAsAHcAcABvACAAcwBoAGEAbABsACAAYgBlACAAcwBjAGEAbABlAGQAIABhAGMAYwBvAHIAZABpAG4AZwBsAHkAJwBcACIAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgBFAEYAXwByAGkAYwBlAHcAcABvAFwAbgBrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5AFwAbgBFAEYAXwB7AHIAaQBjAGUALAB3AHAAbwB9AD0ARQBGAF8AYwBcAFwAdABpAG0AZQBzACAAUwBGAF8AdwBcAFwAdABpAG0AZQBzACAAUwBGAF8AcABcAFwAdABpAG0AZQBzACAAUwBGAF8AbwBcAG4ARQBGAF8AYwAgAD0AIABiAGEAcwBlAGwAaQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBvAG4AdABpAG4AdQBvAHUAcwBsAHkAIABmAGwAbwBvAGQAZQBkACAAZgBpAGUAbABkAHMAIAB3AGkAdABoAG8AdQB0ACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAIAAoAGsAZwAgAEMASAA0AC8AaABhAC8AZABhAHkAKQBcAG4AUwBGAF8AdwAgAD0AIABzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZAB1AHIAaQBuAGcAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABzAGUAYQBzAG8AbgBcAG4AUwBGAF8AcAAgAD0AIABzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAaQBuACAAdABoAGUAIABwAHIAZQAtAHMAZQBhAHMAbwBuAFwAbgBTAEYAXwBvACAAPQAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAB5AHAAZQAgAGEAbgBkACAAYQBtAG8AdQBuAHQAIABvAGYAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAgACgAcwBlAHQAIAB0AG8AIAAxACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB1AHMAZQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBGAF8AYwAsACAAUwBGAF8AdwAsACAAUwBGAF8AcAAsACAAUwBGAF8AbwAsAFwAbgAgACAAIAAgAEUARgBfAGMAIAAqACAAUwBGAF8AdwAgACoAIABTAEYAXwBwACAAKgAgAFMARgBfAG8AXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAF8AcgBpAGMAZQB3AHAAbwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABhAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANwAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwB7AHIAaQBjAGUALAB3AHAAbwB9AD0ARQBGAF8AYwBcAFwAdABpAG0AZQBzACAAUwBGAF8AdwBcAFwAdABpAG0AZQBzACAAUwBGAF8AcABcAFwAdABpAG0AZQBzACAAUwBGAF8AbwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAXwBjAFwAIgAsACAAXAAiAGIAYQBzAGUAbABpAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAG8AbgB0AGkAbgB1AG8AdQBzAGwAeQAgAGYAbABvAG8AZABlAGQAIABmAGkAZQBsAGQAcwAgAHcAaQB0AGgAbwB1AHQAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwBcACIALAAgAFwAIgBrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5AFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGAF8AdwBcACIALAAgAFwAIgBzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZAB1AHIAaQBuAGcAIAB0AGgAZQAgAGcAcgBvAHcAaQBuAGcAIABzAGUAYQBzAG8AbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYAXwBwAFwAIgAsACAAXAAiAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBGAF8AbwBcACIALAAgAFwAIgBzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAeQBwAGUAIABhAG4AZAAgAGEAbQBvAHUAbgB0ACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAANwAuADEALgAxAC4AMQAsACAAKAAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHcAXAAiACwAIABcACIAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABkAHUAcgBpAG4AZwAgAGcAcgBvAHcAaQBuAGcAIABzAGUAYQBzAG8AbgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHAAXAAiACwAIABcACIAcAByAGUALQBzAGUAYQBzAG8AbgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbwBcACIALAAgAFwAIgBvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBcAG4ATwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAIABzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAXABuAFMARgBfAG8AXABuAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXABuAFMARgBfAG8APQAoADEAKwBcAFwAcwB1AG0AXwBvACgAUgBPAEEAXwBvAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwApACkAXgB7ADAALgA1ADkAfQBcAG4AUgBPAEEAXwBvACAAPQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHIAYQB0AGUAIABvAGYAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABvACAAKAB0AG8AbgBuAGUAcwAvAGgAYQApAFwAbgBDAEYATwBBAF8AbwAgAD0AIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABvAGYAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABvAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABSAE8AQQBfAG8ALAAgAEMARgBPAEEAXwBvACwAXABuACAAIAAgACAAKAAxACAAKwAgAFMAVQBNACgAUgBPAEEAXwBvACAAKgAgAEMARgBPAEEAXwBvACkAKQAgAF4AIAAwAC4ANQA5AFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFIATwBBAF8AbwAxACwAIABDAEYATwBBAF8AbwAxACwAIABSAE8AQQBfAG8AMgAsACAAQwBGAE8AQQBfAG8AMgAsACAAUgBPAEEAXwBvADMALAAgAEMARgBPAEEAXwBvADMALAAgAFIATwBBAF8AbwA0ACwAIABDAEYATwBBAF8AbwA0ACwAIABSAE8AQQBfAG8ANQAsACAAQwBGAE8AQQBfAG8ANQAsACAAUgBPAEEAXwBvADYALAAgAEMARgBPAEEAXwBvADYALABcAG4AIAAgACAAIAAoADEAIAArACAAKAAoAFIATwBBAF8AbwAxACAAKgAgAEMARgBPAEEAXwBvADEAKQAgACsAIAAoAFIATwBBAF8AbwAyACAAKgAgAEMARgBPAEEAXwBvADIAKQAgACsAIAAoAFIATwBBAF8AbwAzACAAKgAgAEMARgBPAEEAXwBvADMAKQArACAAKABSAE8AQQBfAG8ANAAgACoAIABDAEYATwBBAF8AbwA0ACkAIAArACAAKABSAE8AQQBfAG8ANQAgACoAIABDAEYATwBBAF8AbwA1ACkAIAArACAAKABSAE8AQQBfAG8ANgAgACoAIABDAEYATwBBAF8AbwA2ACkAKQApACAAXgAgADAALgA1ADkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBfAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA3AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAXwBvAD0AKAAxACsAXABcAHMAdQBtAF8AbwBSAE8AQQBfAG8AXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvACkAXgB7ADAALgA1ADkAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBGAF8AbwA9ACgAMQArACAAKAAoAFIATwBBAF8AbwAxAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwAxACkAIAArACAAKABSAE8AQQBfAG8AMgBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AMgApACAAKwAgACgAUgBPAEEAXwBvADMAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADMAKQAgACsAIAAoAFIATwBBAF8AbwA0AFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwA0ACkAIAArACAAKABSAE8AQQBfAG8ANQBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8ANQApACAAKwAgACgAUgBPAEEAXwBvADYAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADYAKQApAF4AewAwAC4ANQA5AH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAE8AQQBfAG8AXAAiACwAIABcACIAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAcgBhAHQAZQAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAG8AXAAiACwAIABcACIAdABvAG4AbgBlAHMALwBoAGEAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYATwBBAF8AbwBcACIALAAgAFwAIgBjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABvAGYAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABvAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAG8AXAAiACwAIABcACIAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AYwBsAHUAZABlAGQAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGEAcwAgAHAAZQByACAAVgBFAEUAUgBHACAAZQBxAHUAYQB0AGkAbwBuACAAZABlAHMAYwByAGkAcAB0AGkAbwBuADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAaABlAHIAZQAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGkAcwAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIAB0AGgAZQAgAHIAaQBjAGUAIABmAGkAZQBsAGQAcwAgAHIAYQB0AGgAZQByACAAdABoAGEAbgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACwAIABTAEYAXwBvACAAaQBzACAAcwBlAHQAIAB0AG8AIAAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGwAYQByAGUAZAAgAGUAYQBjAGgAIABhAG0AZQBuAGQAbQBlAG4AdAAgAHMAZQBwAGEAcgBhAHQAZQBsAHkAIAB0AG8AIABhAGwAbABvAHcAIABzAHUAbQBtAGkAbgBnACAAaQBuACAARQB4AGMAZQBsACAAaQBuACAAbwBuAGUAIABlAHEAdQBhAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQBdACwAIgBwAHIAbwBqAGUAYwB0AE4AYQBtAGUAcwAiADoAWwAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAFIAbwB3AFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATwBuAGUAQwBvAGwAdQBtAG4AQQBuAGQASABlAGEAZABlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5ACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABOADIATwBFAEYARgByAG8AbQBQAHIAbwBkAEkAcgByAGkAZwBhAHQAaQBvAG4AUgBhAGkAbgBmAGEAbABsACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBDAG8AbgB2AGUAcgB0AFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAFQAbwBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8ARABhAHQAYQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAFUAbgBpAHQAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8ARABhAHQAYQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8ARABhAHQAYQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFUAbgBpAHQAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8ARABhAHQAYQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBVAG4AaQB0ACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlACAAZABhAHQAYQAgAHQAaABhAHQAIABpAHMAIABjAG8AbQBtAG8AbgAgAGEAYwByAG8AcwBzACAAYQBsAGwAIABlAG4AdABlAHIAcAByAGkAcwBlACAAdAB5AHAAZQBzAFwAbgBFAHgAYwBlAGwAIABtAG8AZAB1AGwAZQAgAG4AYQBtAGUAOgAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBcAG4AcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgACgAMAAuADYANwA4ADQAIABrAGcALwBtADMAKQBcAG4AVABhAGsAZQBuACAAZgByAG8AbQAgAHQAaABlACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAGEAbgBkACAARQBuAGUAcgBnAHkAIABSAGUAcABvAHIAdABpAG4AZwAgAFwAbgAoAE0AZQBhAHMAdQByAGUAbQBlAG4AdAApACAARABlAHQAZQByAG0AaQBuAGEAdABpAG8AbgAgADIAMAAwADgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAcAAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAG0AMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuAHMAIAAzAC4AQgAuADEAYQBfADIALAAgADMALgBCAC4AMQBjAF8AMgAsACAAMwAuAEIALgAzAF8AMQAsACAAMwAuAEIALgA0AGcAXwAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4ANgA3ADgANAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXABuAEMAZwAgAD0AIAA0ADQALwAyADgAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAA0ADQALwAyADgAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXABuAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGcAYQBzACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAZwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADEAXAAiACwAIABcACIAQwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPADIAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIABcACIAMQA2AC8AMQAyAFwAIgAsACAAMQA2ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIABcACIANAA0AC8AMgA4AFwAIgAsACAANAA0ACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHgAXAAiACwAIABcACIANAA2AC8AMQA0AFwAIgAsACAANAA2ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAXAAiADIAOAAvADEAMgBcACIALAAgADIAOAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyACAATABpAG0AZQBcACIALAAgAFwAIgA0ADQALwAxADIAXAAiACwAIAA0ADQALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAE0AVgBPAEMAXAAiACwAIABcACIAMQA0AC8AMQAyAFwAIgAsACAAMQA0ACwAIAAxADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAE4AMgBPAFwAbgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABOADIATwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAGEAYwB0AG8AcgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBPADIALQBlACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEgANABcACIALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgA0AFwAIgAsACAANgA2ADMAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDADIARgA2AFwAIgAsACAAMQAyADIAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgA2AFwAIgAsACAAMgAyADgAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4ARgAzAFwAIgAsACAAMQA3ADIAMAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAHQAYQB0AGUAcwAgAGEAbgBkACAAdABlAHIAcgBpAHQAbwByAGkAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEMAbwBtAG0AbwBuACAATgBhAG0AZQBcACIALAAgAFwAIgBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABDAGEAcABpAHQAYQBsACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBJAEMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBRAEwARABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAUwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAEEAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIATgBUAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAEIAUwAgAFMAdABhAHQAaQBzAHQAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAA0ACAALQAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQgB1AHIAZQBhAHUAIABvAGYAIABTAHQAYQB0AGkAcwB0AGkAYwBzACAAKABBAEIAUwApACAALQAgAFMAdABhAHQAaQBzAHQAaQBjAGEAbAAgAEEAcgBlAGEAcwAgAEwAZQB2AGUAbAAgADIAIAAtACAAMgAwADIAMQAgAC0AIABTAGgAYQBwAGUAZgBpAGwAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBACAANAAgAE4AYQBtAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAdQBuAGIAdQByAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAGQAdQByAGEAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAEkAbgBuAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAE4AbwByAHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAAUwBvAHUAdABoACAARQBhAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABXAGgAZQBhAHQAIABCAGUAbAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgATgBvAHIAdABoACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABPAHUAdABiAGEAYwBrACAAKABTAG8AdQB0AGgAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADIAOgAgAFQAcgBhAG4AcwBsAGEAdABpAG4AZwAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAIAB0AG8AIAB3AGUAdAAgAGEAbgBkACAAZAByAHkAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIAAtACAAQwBoAGEAbgBnAGUAZAAgAFwAdQAwADAAMgA3AEYAcgB5AFwAdQAwADAAMgA3ACAAdABvACAAXAB1ADAAMAAyADcARAByAHkAXAB1ADAAMAAyADcALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAFoAbwBuAGUAXAAiACwAIABcACIAVwBlAHQAIABvAHIAIABEAHIAeQAgAFoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABoAGkAZwBoACAAdABlAG0AcABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAHcAYQByAG0AIAAvACAAYwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALwAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0ACAAYQBuAGQAIABoAGkAZwBoACAAdABlAG0AcAAgAGMAbABhAHMAcwBlAHMAIAB0AG8AIABhAGMAYwBvAG0AbQBvAGQAYQB0AGUAIABjAGwAaQBtAGEAdABlACAAcwBjAGUAbgBhAHIAaQBvAHMAIABlAHgAYwBsAHUAZABlAGQAIABiAHkAIABWAEUARQBSAEcAIABjAHIAaQB0AGUAcgBpAGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBpAHgAZQBkACAAdAB5AHAAbwAgAGkAbgAgAE0AQQBUACAAdgBhAGwAdQBlACAAZgBvAHIAIAB3AGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABjAGgAYQBuAGcAZQBkACAAMQAwACAAdABvACAAMQAxAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAG0AaQBuACAAYQBuAGQAIABtAGEAeAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAE0AQQBUACwAIABNAEEAUAAsACAAZgByAG8AcwB0ACAAZABhAHkAcwAgAHAAZQByACAAeQBlAGEAcgAsACAAZQBsAGUAdgBhAHQAaQBvAG4ALAAgAE0AQQBQADoAUABFAFQAIAB0AG8AIABjAGEAbABjAHUAbABhAHQAZQAgAHoAbwBuAGUAcwAgAGYAcgBvAG0AIAByAGUAYQBsACAAYwBsAGkAbQBhAHQAZQAgAGQAYQB0AGEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBBAEYAIABhAGMAYwBlAHAAdABzACAAcgBhAGkAbgBmAGEAbABsACAAYQBzACAAYQAgAHAAcgBvAHgAeQAgAGYAbwByACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUAFwAIgAsACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAEYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIAXAAiACwAIABcACIARQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAHQAZQBtAHAAXAAiACwAIABcACIATQBhAHgAIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AaQBuACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAE0AaQBuACAAZgByAG8AcwB0ACAAZABhAHkAcwBcACIALAAgAFwAIgBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBpAG4AIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFAAOgBQAEUAVABcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBuAHQAYQBuAGUAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAxADAAMAAwACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAdwBlAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMgAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgADIAMAAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAG0AIAAtACAAZCIgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAxADAAMAAwAC4AMAAwADEALAAgADIAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAG8AcABpAGMAYQBsACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADgAIABDAFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkALgA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQBcACIALAAgADEAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAMQAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAwACAAQwAgAC0AIABkIiAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAAMQBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAAIAAtADkAOQA5ADkAOQA5ACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB0AGUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFQAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUAAgAD0AIABtAGUAYQBuACAAYQBuAG4AdQBhAGwAIABwAHIAZQBjAGkAcABpAHQAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAEUAVAAgAD0AIABwAG8AdABlAG4AdABpAGEAbAAgAGUAdgBhAHAAbwB0AHIAYQBuAHMAcABpAHIAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAE0AQQBUACAAbQBpAG4AIABhAG4AZAAgAE0AQQBUACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAE0AZQBkAGkAYQBuACAAQQBuAG4AdQBhAGwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAAoAE0AQQBUACkAXAAiACwAIABcACIATQBpAG4AIABNAEEAVABcACIALAAgAFwAIgBNAGEAeAAgAE0AQQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiIAAyADYAIABDAFwAIgAsACAAMgA2ACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgAFwAIgAxADUAIAAtACAAMgA1ACAAQwBcACIALAAgADEANQAsACAAMgA1AC4AOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIiAAMQA0ACAAQwBcACIALAAgAC0AOQA5ADkAOQA5ADkALAAgADEANAAuADkAOQA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlACAAZgByAG8AbQAgAHIAZQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkAGEAdABhAC4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABaAG8AbgBlAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AaQBuAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgAsACAAXAAiAEEAbgBuAHUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAXAB1ADAAMAAzAGUAIAA2ADAAMABtAG0AXAAiACwAIAA2ADAAMAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAGQiIAA2ADAAMABtAG0AXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAA2ADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAXABuACAAIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAFoAbwBuAGUAXAAiACwAIABcACIATABlAGEAYwBoAGkAbgBnACAAYwByAGkAdABlAHIAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABvAGMAYwB1AHIAcwBcACIALAAgAFwAIgCjAygANdhf3DXYTtw12FbcNdhb3CkAXAB1ADAAMAAzAGUAowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABkAG8AZQBzACAAbgBvAHQAIABvAGMAYwB1AHIAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAGQiowMoADXYONw12EfcMAApACsANdhg3DXYXNw12FbcNdhZ3CAANdhk3DXYTtw12GHcNdhS3DXYX9wgAA4hNdhc3DXYWdw12FHcNdhW3DXYW9w12FTcIAA12FDcNdhO3DXYXdw12E7cNdhQ3DXYVtw12GHcNdhm3FwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBzACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAWQBlAHMAIAAtACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvACAALQAgAG4AbwB0ACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQBcACIALAAgADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAZABhAHQAYQAgAHMAYwBvAHIAZQBzACAAZgBvAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFgAWABYAFgAWABYAFgAWABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABhACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIARABhAHQAYQAgAHMAYwBvAHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBuAHQAZQByAG4AYQB0AGkAbwBuAGEAbAAgAHMAYwBvAHAAZQAgADMAIABkAGEAdABhAGIAYQBzAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAIABvAHIAIAByAGUAZwBpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGkAbgB0AGUAbgBzAGkAdAB5ACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIABhAHAAcAByAG8AdgBlAGQAIABtAGUAdABoAG8AZABcACIALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBlAHIAaQBmAGkAZQBkACAAYwByAGUAZABlAG4AdABpAGEAbAAgAG0AYQB0AGMAaABpAG4AZwAgAEkAUwBPADEANAAwADYANwBcACIALAAgADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAMAAuADIANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBcAG4AVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApACAAKABFAEYATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAXAAiACwAXAAiAEUARgBOADIATwBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAA1ADkALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAMAAuADAAMAA3ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABsAG8AdwAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAMgA5ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAApAFwAIgAsADAALgAwADAAOAAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAMAAuADAAMQA5ADkALAAgAFwAIgBTAHUAZwBhAHIAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsADAALgAwADAANQAzACwAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAMAAuADAAMAA2ADQALAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABjAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnACkAXAAiACwAMAAuADAAMAAzACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBDAG8AbgB0AGkAbgB1AG8AdQBzACAAZgBsAG8AbwBkAGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlACAAKABzAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnACkAXAAiACwAMAAuADAAMAA1ACwAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAGEAbgBkACAAbQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACwAIABvAHIAIABhAGwAdABlAHIAbgBhAHQAZQAgAHcAZQB0AHQAaQBuAGcAIABhAG4AZAAgAGQAcgB5AGkAbgBnAFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAMAAuADAAMAAyADYALAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAEYAbwByAGUAcwB0AHIAeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABkAHUAcABsAGkAYwBhAHQAZQAgAFwAdQAwADAAMgA3AEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAZQBtAG8AdgBlAGQAIABhAHMAdABlAHIAaQBzAGsAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAaQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AG4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcAIAB3AGkAdABoACAAcwBhAG0AZQAgAEUARgAgAGYAbwByACAAbABvAHcAIABhAG4AZAAgAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXABuAEkAUABDAEMAOgAgAE4AMgBPACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATQBBAE4AQQBHAEUARAAgAFMATwBJAEwAUwAsACAAQQBOAEQAIABDAE8AMgAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAEwASQBNAEUAIABBAE4ARAAgAFUAUgBFAEEAIABBAFAAUABMAEkAQwBBAFQASQBPAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByAFwAIgAsAFwAIgBGAHIAYQBjAFcARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAHIAaQBuAGsAbABlAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcgBmAGEAYwBlACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABUAGEAYgBsAGUAIABjAHIAZQBhAHQAZQBkACAAYgBhAHMAZQBkACAAbwBuACAAVgBFAEUAUgBHACAAdABlAHgAdAAgAFwAdQAwADAAMgA3AEEAcgBlAGEAcwAgAGEAcgBlACAAcwB1AGIAagBlAGMAdAAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgACgAaQAuAGUALgAsACAAaQBuACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACkAIAB3AGgAZQBuAC4ALgAuACAAdABoAGUAIABsAGEAbgBkACAAaQBzACAAaQByAHIAaQBnAGEAdABlAGQAIAAoAGUAeABjAGUAcAB0ACAAZAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AKQAuAFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADIAOgAgAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAFAAUgBQACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAG8AcgAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgAyAE8AIAAtACAATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIABcACIARQBGAFAAUgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAB1ADAAMAAyADcAIAB0AG8AIABzAGkAbgBnAHUAbABhAHIAIABcAHUAMAAwADIANwBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbwBuAHQAaABzACAAdABvACAAUwBlAGEAcwBvAG4AcwAgAE0AYQBwAHAAaQBuAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AbgB0AGgAXAAiACwAIABcACIAUwBlAGEAcwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEoAYQBuAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBiAHIAdQBhAHIAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAHIAYwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAcgBpAGwAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbgBlAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAHUAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAZwB1AHMAdABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAHAAdABlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AYwB0AG8AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB2AGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAbgB1AHIAZQAgAE0AYQBuAGEAZwBlAG0AZQBuAHQAIAATICAATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHAAZQByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA4AC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAAxADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAXAAiACwAIABcACIATQBBAFQAIAAoALoAQwApAFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAUwBsAHUAcgByAHkAIAAoAHcAaQB0AGgAbwB1AHQAIABuAGEAdAB1AHIAYQBsACAAYwByAHUAcwB0ACkAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAGIAKQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABTAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAMQAgAG0AbwBuAHQAaABcACIALAAgAFwAIgBEAGUAZQBwACAATABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlACAAKAB3AGkAdABoAC8AdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACkAXAAiACwAIABcACIAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAaQBuAHQAbwAgAHAAZQBsAGwAZQB0AGkAegBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACwAIABSAGEAbgBnAGUAIABhAG4AZAAgAFAAYQBkAGQAbwBjAGsAIAAoAGMAKQAoAGQAKQBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAXAAiAGQiMQAwAFwAIgAsACAAMAAuADYANgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMQAsACAAMAAuADYAOAAsACAAMAAuADEALAAgADAALgAxADEALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAyACwAIAAwAC4ANwAsACAAMAAuADEALAAgADAALgAxADMALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQAzACwAIAAwAC4ANwAxACwAIAAwAC4AMQAsACAAMAAuADEANAAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADQALAAgADAALgA3ADMALAAgADAALgAxACwAIAAwAC4AMQA1ACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADUALAAgADAALgA3ADQALAAgADAALgAxACwAIAAwAC4AMQA3ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA2ACwAIAAwAC4ANwA1ACwAIAAwAC4AMQAsACAAMAAuADEAOAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANwAsACAAMAAuADcANgAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA4ACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAsACAAMAAuADIAMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOQAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADQALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADAALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMgA2ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAxACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIAOQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMgAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAzADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADMALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4AMwA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgA0ACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANQAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADEALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANgAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgA0ADQALAAgADAALgAwADEALAAgADAALgAwADEANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgADIANwAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANAA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIABcACIAZSIyADgAXAAiACwAIAAwAC4AOAAsACAAMAAuADEALAAgADAALgA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwBcACIALAAgAFwAIgBEAGEAaQBsAHkAIABzAHAAcgBlAGEAZABcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBNAEEAVAAgAHIAYQB3AFwAIgAgAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAcgBvAHcAIABvAGYAIABOAEkAUgAgAE0ATQBBACAAZABlAGYAaQBuAGkAdABpAG8AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuACAARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIAB3AGkAdABoACAAYQBuAGQAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGUAcABhAHIAYQB0AGUAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE0AQQBUACAAcgBhAHcAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAbABsAG8AdwAgAGwAbwBvAGsAdQBwACAAbwBmACAAbgB1AG0AYgBlAHIAcwAuAFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AaQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMgAuADEALgA0AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBOAGkAIABcAHUAMAAwADIANgAgAEUARgBOADIATwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAFQAdwBvAEMAbwBsAHUAbQBuAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABbAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlAF0ALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAMQAsACAAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACkAKgAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlADIAKQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAEYARgBhAGwAcwBlACkAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE8AbgBlAEMAbwBsAHUAbQBuAEEAbgBkAEgAZQBhAGQAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBmAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlADIALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQAsACAAXAAiAFwAIgAsACAAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBwAGwAaQB0AFMAdAByAGkAbgBnAEkAbgB0AG8AQQByAHIAYQB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsACAARABlAGwAaQBtAGkAdABlAHIALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEAXQAsACAAWwBDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgBdACwAXABuACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgBYAE0ATAAoAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAHQAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAIABcAHUAMAAwADIANgBcAG4AIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUwBVAEIAUwBUAEkAVABVAFQARQAoAFMAVQBCAFMAVABJAFQAVQBUAEUAKABDAGUAbABsACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADEALABcACIAXAAiACkALABDAGgAYQByAGEAYwB0AGUAcgBUAG8AUgBlAG0AbwB2AGUAMgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABEAGUAbABpAG0AaQB0AGUAcgAsAFwAIgBcAHUAMAAwADMAYwAvAHMAXAB1ADAAMAAzAGUAXAB1ADAAMAAzAGMAcwBcAHUAMAAwADMAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAApACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAC8AdABcAHUAMAAwADMAZQBcACIALABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAvAC8AcwBcACIAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEMAbABpAG0AYQB0AGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAGEAdgBnAFQAZQBtAHAALABhAHYAZwBSAGEAaQBuACwAZgByAG8AcwB0AEQAYQB5AHMALABlAGwAZQB2ACwAbQBhAHAAXwBwAGUAdAAsAFwAbgAgACAAIAAgAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACwAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACwAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkALABtAGEAeABGAHIAbwBzAHQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUABFAFQAQQByAHIAYQB5ACwAbQBhAHgAUABFAFQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAYwBsAGkAbQBhAHQAZQBaAG8AbgBlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAVABlAG0AcABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFQAZQBtAHAAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBSAGEAaQBuAGYAYQBsAGwAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBhAHYAZwBSAGEAaQBuACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AaQBuAEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABFAGwAZQB2AGEAdABpAG8AbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AG0AYQBwAF8AcABlAHQAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGEAeABQAEUAVABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AG0AYQBwAF8AcABlAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ARwBlAHQARgByAGEAYwBXAEUAVABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEwAbwBvAGsAdQBwACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVAAsACAAXABuACAAIAAgACAAIAAgACAAIABDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcABcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQAIAArACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAFwAdQAwADAAMwBlADAALAAgADEALAAgADAAKQBcAG4AIAAgACAAIAApACkAOwBcAG4AXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AQwBvAG4AdgBlAHIAdABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBUAG8AQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsAFwAbgAgACAAIAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQAsACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAG8AdQByAGMAZQBIAHkAcABlAHIAbABpAG4AawBcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAdQAwADAAMgA3AFwAIgAgAFwAdQAwADAAMgA2ACAAcwBoACAAXAB1ADAAMAAyADYAIABcACIAXAB1ADAAMAAyADcAIQBcACIAIABcAHUAMAAwADIANgAgAGEAZABkAHIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsARABpAGYAZgBlAHIAZQBuAHQAUwBoAGUAZQB0AFwAbgA9AEwAQQBNAEIARABBACgAVABhAHIAZwBlAHQAQwBlAGwAbAAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABzAGgALAAgAFQARQBYAFQAQQBGAFQARQBSACgAQwBFAEwATAAoAFwAIgBmAGkAbABlAG4AYQBtAGUAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALAAgAFwAIgBdAFwAIgApACwAXABuACAAIAAgACAAYQBkAGQAcgAsACAAQwBFAEwATAAoAFwAIgBhAGQAZAByAGUAcwBzAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAXABuACAAIAAgACAAXAAiACMAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAxAF8AMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADEALAAgADIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAGcAdQBtAGUAbgB0AHMAXwAzAF8ANABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEEAcgBnAHUAbQBlAG4AdABzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEMASABPAE8AUwBFAEMATwBMAFMAKABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALAAgADMALAAgADQAKQBcAG4AKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBHAGUAdABNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAATQBNAFMALAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALAAgAE0ATQBTAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATQBFAEQASQBBAE4AKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAYgBhAHMAZQBkACAAbwBuACAAdABoAGUAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGUAbQBwAGwAbwB5AGUAZAAgAGQAdQByAGkAbgBnACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcwBlAGEAcwBvAG4AIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIABwAGUAcgBpAG8AZABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBGAHcAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAzAC4AMQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHQAeQBwAGUAXAAiACwAIABcACIAVwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABzAHUAYgAgAC0AIAB0AHkAcABlAFwAIgAsACAAXAAiAFMARgB3AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBVAHAAbABhAG4AZABcACIALAAgAFwAIgBQAGEAZABkAHkAIAByAG8AdABhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFUAcABsAGEAbgBkAFwAIgAsACAAXAAiAEYAYQBsAGwAbwB3ACAAdwBpAHQAaABvAHUAdAAgAGYAbABvAG8AZABpAG4AZwAgAGkAbgAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZABcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABkAHIAYQBpAG4AYQBnAGUAIABwAGUAcgBpAG8AZABcACIALAAgADAALgA3ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATQB1AGwAdABpAHAAbABlACAAZAByAGEAaQBuAGEAZwBlACAAcABlAHIAaQBvAGQAcwBcACIALAAgADAALgA1ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGUAZAAgAGEAbgBkACAAZABlAGUAcAAgAHcAYQB0AGUAcgBcACIALAAgAFwAIgBSAGUAZwB1AGwAYQByACAAcgBhAGkAbgBmAGUAZABcACIALAAgADAALgA1ADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGUAZAAgAGEAbgBkACAAZABlAGUAcAAgAHcAYQB0AGUAcgBcACIALAAgAFwAIgBEAHIAbwB1AGcAaAB0ACAAcAByAG8AbgBlAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGEAaQBuAGYAZQBkACAAYQBuAGQAIABkAGUAZQBwACAAdwBhAHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIAB3AGEAdABlAHIAXAAiACwAIAAwAC4AMAA2AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAIABiAGEAcwBlAGQAIABvAG4AIAB0AGgAZQAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAZQBtAHAAbABvAHkAZQBkACAAaQBuACAAdABoAGUAIABwAHIAZQAgAC0AIABzAGUAYQBzAG8AbgAgAGIAZQBmAG8AcgBlACAAdABoAGUAIABnAHIAbwB3AGkAbgBnACAAcABlAHIAaQBvAGQAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAcABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMwAuADIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAHAAcgBpAG8AcgAgAHQAbwAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkACAAcABcACIALAAgAFwAIgBTAEYAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4AIABmAGwAbwBvAGQAZQBkACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAFwAdQAwADAAMwBjADEAOAAwACAAZABhAHkAcwBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4AIABmAGwAbwBvAGQAZQBkACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAFwAdQAwADAAMwBlADEAOAAwACAAZABhAHkAcwBcACIALAAgADAALgA4ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBsAG8AbwBkAGUAZAAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AIABcAHUAMAAwADMAZQAzADAAIABkAGEAeQBzAFwAIgAsACAAMgAuADQAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGYAbABvAG8AZABlAGQAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAXAB1ADAAMAAzAGUAMwA2ADUAIABkAGEAeQBzAFwAIgAsACAAMAAuADUAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAaQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAEYATwBBAGkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMwAuADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBjAGwAdQBkAGUAZAAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAYQBzACAAcABlAHIAIABWAEUARQBSAEcAIABlAHEAdQBhAHQAaQBvAG4AIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAcgBlACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAaQBzACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHQAaABlACAAcgBpAGMAZQAgAGYAaQBlAGwAZABzACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMALAAgAFMARgBfAG8AIABpAHMAIABzAGUAdAAgAHQAbwAgADEALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABpAFwAIgAsACAAXAAiAEMARgBPAEEAaQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AHIAYQB3ACAAaQBuAGMAbwByAHAAbwByAGEAdABlAGQAIABzAGgAbwByAHQAbAB5ACAAKABcAHUAMAAwADMAYwAzADAAIABkAGEAeQBzACkAIABiAGUAZgBvAHIAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgBcACIALAAgADEALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AHIAYQB3ACAAaQBuAGMAbwByAHAAbwByAGEAdABlAGQAIABsAG8AbgBnACAAKABcAHUAMAAwADMAZQAzADAAIABkAGEAeQBzACkAIABiAGUAZgBvAHIAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgBcACIALAAgADAALgAxADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG0AcABvAHMAdABcACIALAAgADAALgAxADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBhAHIAbQAgAHkAYQByAGQAIABtAGEAbgB1AHIAZQBcACIALAAgADAALgAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwByAGUAZQBuACAAbQBhAG4AdQByAGUAXAAiACwAIAAwAC4ANAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAYQBzAGUAbABpAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAG8AbgB0AGkAbgB1AG8AdQBzAGwAeQAgAGYAbABvAG8AZABlAGQAIABmAGkAZQBsAGQAcwAgAHcAaQB0AGgAbwB1AHQAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAGMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAgAC8AIABoAGEAIAAvACAAZABhAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANwAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMQAuADEAOQApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA3AC4AMQA6ACAAUgBpAGMAZQAgAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANwAuADEALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABSAGkAYwBlACAAQwB1AGwAdABpAHYAYQB0AGkAbwBuACAAQwBIADQAIABFAG0AaQBzAHMAaQBvAG4AcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAbgBFAF8AcgBpAGMAZQBcAG4AdAAgAEMASAA0AFwAbgBFAF8AewByAGkAYwBlAH0APQBcAFwAcwB1AG0AXwB3AFwAXABzAHUAbQBfAHAAXABcAHMAdQBtAF8AbwAoAEEAXwB7AHIAaQBjAGUALAB3AHAAbwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AHIAaQBjAGUALAB3AHAAbwB9AFwAXAB0AGkAbQBlAHMAIAB0AF8AewByAGkAYwBlACwAdwBwAG8AfQApAFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AFwAbgBBAF8AcgBpAGMAZQB3AHAAbwAgAD0AIABhAG4AbgB1AGEAbAAgAGEAcgBlAGEAIABvAGYAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuACAAdQBuAGQAZQByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIAB3ACwAIABwAHIAZQAtAHMAZQBhAHMAbwBuACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABwACwAIABhAG4AZAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAGMAbwBuAGQAaQB0AGkAbwBuACAAbwAgACgAaABhACkAXABuAEUARgBfAHIAaQBjAGUAdwBwAG8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIAB1AG4AZABlAHIAIABjAG8AbgBkAGkAdABpAG8AbgBzACAAdwAsACAAcAAsACAAYQBuAGQAIABvACAAKABrAGcAIABDAEgANAAvAGgAYQAvAGQAYQB5ACkAXABuAHQAXwByAGkAYwBlAHcAcABvACAAPQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHAAZQByAGkAbwBkACAAZgBvAHIAIAByAGkAYwBlACAAdQBuAGQAZQByACAAYwBvAG4AZABpAHQAaQBvAG4AcwAgAHcALAAgAHAALAAgAGEAbgBkACAAbwAgACgAZABhAHkAcwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBfAHIAaQBjAGUAdwBwAG8ALAAgAEUARgBfAHIAaQBjAGUAdwBwAG8ALAAgAHQAXwByAGkAYwBlAHcAcABvACwAXABuACAAIAAgACAAUwBVAE0AKABBAF8AcgBpAGMAZQB3AHAAbwAgACoAIABFAEYAXwByAGkAYwBlAHcAcABvACAAKgAgAHQAXwByAGkAYwBlAHcAcABvACkAIAAqACAAMQAwACAAXgAgAC0AMwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AcgBpAGMAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA3AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AHIAaQBjAGUAfQA9AFwAXABzAHUAbQBfAHcAXABcAHMAdQBtAF8AcABcAFwAcwB1AG0AXwBvACgAQQBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0AXABcAHQAaQBtAGUAcwAgAHQAXwB7AHIAaQBjAGUALAB3AHAAbwB9ACkAXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADQALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBfAHIAaQBjAGUAdwBwAG8AXAAiACwAIABcACIAYQBuAG4AdQBhAGwAIABhAHIAZQBhACAAbwBmACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHUAbgBkAGUAcgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAdwAsACAAcAByAGUALQBzAGUAYQBzAG8AbgAgAHcAYQB0AGUAcgAgAHIAZQBnAGkAbQBlACAAcAAsACAAYQBuAGQAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIABjAG8AbgBkAGkAdABpAG8AbgAgAG8AXAAiACwAIABcACIAaABhAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAF8AcgBpAGMAZQB3AHAAbwBcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcgBpAGMAZQAgAGMAdQBsAHQAaQB2AGEAdABpAG8AbgAgAHUAbgBkAGUAcgAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAIAB3ACwAIABwACwAIABhAG4AZAAgAG8AXAAiACwAIABcACIAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcACIALAAgAFwAIgBDAGEAbABjAHUAbABhAHQAZQBkACAAZgByAG8AbQAgADcALgAxAC4AMQAuADEALAAgACgAMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB0AF8AcgBpAGMAZQB3AHAAbwBcACIALAAgAFwAIgBjAHUAbAB0AGkAdgBhAHQAaQBvAG4AIABwAGUAcgBpAG8AZAAgAGYAbwByACAAcgBpAGMAZQAgAHUAbgBkAGUAcgAgAGMAbwBuAGQAaQB0AGkAbwBuAHMAIAB3ACwAIABwACwAIABhAG4AZAAgAG8AXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHMAXAAiACwAIABcACIAbgB1AG0AYgBlAHIAIABvAGYAIABjAHIAbwBwAHAAaQBuAGcAIABzAGUAYQBzAG8AbgBzACAAaQBuACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAG0AYQBuAGEAZwBlAGQAIAB0AGgAaQBzACAAdwBhAHkAXAAiACwAIABcACIAcwBlAGEAcwBvAG4AcwBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AG4AdQBtAGIAZQByACAAbwBmACAAcwBlAGEAcwBvAG4AcwBcAHUAMAAwADIANwAgAHYAYQByAGkAYQBiAGwAZQAgAGEAcwAgAHAAZQByACAAVgBFAEUAUgBHACAAZABlAHMAYwByAGkAcAB0AGkAbwBuACAAaQBuACAANwAuADIALgAxACAAXAB1ADAAMAAyADcAVwBoAGUAcgBlACAAdABoAGUAcgBlACAAaQBzACAAbQBvAHIAZQAgAHQAaABhAG4AIABvAG4AZQAgAGMAcgBvAHAAcABpAG4AZwAgAHMAZQBhAHMAbwBuACAAcABlAHIAIAB5AGUAYQByACwAIABBAHIAaQBjAGUALAB3AHAAbwAgAHMAaABhAGwAbAAgAGIAZQAgAHMAYwBhAGwAZQBkACAAYQBjAGMAbwByAGQAaQBuAGcAbAB5AFwAdQAwADAAMgA3AFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHIAaQBjAGUAIABjAHUAbAB0AGkAdgBhAHQAaQBvAG4AXABuAEUARgBfAHIAaQBjAGUAdwBwAG8AXABuAGsAZwAgAEMASAA0AC8AaABhAC8AZABhAHkAXABuAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0APQBFAEYAXwBjAFwAXAB0AGkAbQBlAHMAIABTAEYAXwB3AFwAXAB0AGkAbQBlAHMAIABTAEYAXwBwAFwAXAB0AGkAbQBlAHMAIABTAEYAXwBvAFwAbgBFAEYAXwBjACAAPQAgAGIAYQBzAGUAbABpAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAG8AbgB0AGkAbgB1AG8AdQBzAGwAeQAgAGYAbABvAG8AZABlAGQAIABmAGkAZQBsAGQAcwAgAHcAaQB0AGgAbwB1AHQAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAgACgAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQApAFwAbgBTAEYAXwB3ACAAPQAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABkAHUAcgBpAG4AZwAgAHQAaABlACAAZwByAG8AdwBpAG4AZwAgAHMAZQBhAHMAbwBuAFwAbgBTAEYAXwBwACAAPQAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBlAC0AcwBlAGEAcwBvAG4AXABuAFMARgBfAG8AIAA9ACAAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHkAcABlACAAYQBuAGQAIABhAG0AbwB1AG4AdAAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAKABzAGUAdAAgAHQAbwAgADEAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHUAcwBlACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAEYAXwBjACwAIABTAEYAXwB3ACwAIABTAEYAXwBwACwAIABTAEYAXwBvACwAXABuACAAIAAgACAARQBGAF8AYwAgACoAIABTAEYAXwB3ACAAKgAgAFMARgBfAHAAIAAqACAAUwBGAF8AbwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAByAGkAYwBlACAAYwB1AGwAdABpAHYAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEYAXwByAGkAYwBlAHcAcABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGEALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA3AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUARgBfAHsAcgBpAGMAZQAsAHcAcABvAH0APQBFAEYAXwBjAFwAXAB0AGkAbQBlAHMAIABTAEYAXwB3AFwAXAB0AGkAbQBlAHMAIABTAEYAXwBwAFwAXAB0AGkAbQBlAHMAIABTAEYAXwBvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBfAGMAXAAiACwAIABcACIAYgBhAHMAZQBsAGkAbgBlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAbwBuAHQAaQBuAHUAbwB1AHMAbAB5ACAAZgBsAG8AbwBkAGUAZAAgAGYAaQBlAGwAZABzACAAdwBpAHQAaABvAHUAdAAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAIgAsACAAXAAiAGsAZwAgAEMASAA0AC8AaABhAC8AZABhAHkAXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYAXwB3AFwAIgAsACAAXAAiAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAIABkAHUAcgBpAG4AZwAgAHQAaABlACAAZwByAG8AdwBpAG4AZwAgAHMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIALAAgAFwAIgBDAG8AbgBzAHQAYQBuAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMARgBfAHAAXAAiACwAIABcACIAcwBjAGEAbABpAG4AZwAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGkAbgAgAHQAaABlACAAcAByAGUALQBzAGUAYQBzAG8AbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBvAG4AcwB0AGEAbgB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYAXwBvAFwAIgAsACAAXAAiAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAB5AHAAZQAgAGEAbgBkACAAYQBtAG8AdQBuAHQAIABvAGYAIABvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIABcACIAQwBhAGwAYwB1AGwAYQB0AGUAZAAgAGYAcgBvAG0AIAA3AC4AMQAuADEALgAxACwAIAAoADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAdwBcACIALAAgAFwAIgB3AGEAdABlAHIAIAByAGUAZwBpAG0AZQAgAGQAdQByAGkAbgBnACAAZwByAG8AdwBpAG4AZwAgAHMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcABcACIALAAgAFwAIgBwAHIAZQAtAHMAZQBhAHMAbwBuACAAdwBhAHQAZQByACAAcgBlAGcAaQBtAGUAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAHAAdQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBvAFwAIgAsACAAXAAiAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFwAbgBPAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAgAHMAYwBhAGwAaQBuAGcAIABmAGEAYwB0AG8AcgBcAG4AUwBGAF8AbwBcAG4AZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcAG4AUwBGAF8AbwA9ACgAMQArAFwAXABzAHUAbQBfAG8AKABSAE8AQQBfAG8AXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvACkAKQBeAHsAMAAuADUAOQB9AFwAbgBSAE8AQQBfAG8AIAA9ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAcgBhAHQAZQAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAG8AIAAoAHQAbwBuAG4AZQBzAC8AaABhACkAXABuAEMARgBPAEEAXwBvACAAPQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAG8AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFIATwBBAF8AbwAsACAAQwBGAE8AQQBfAG8ALABcAG4AIAAgACAAIAAoADEAIAArACAAUwBVAE0AKABSAE8AQQBfAG8AIAAqACAAQwBGAE8AQQBfAG8AKQApACAAXgAgADAALgA1ADkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUgBPAEEAXwBvADEALAAgAEMARgBPAEEAXwBvADEALAAgAFIATwBBAF8AbwAyACwAIABDAEYATwBBAF8AbwAyACwAIABSAE8AQQBfAG8AMwAsACAAQwBGAE8AQQBfAG8AMwAsACAAUgBPAEEAXwBvADQALAAgAEMARgBPAEEAXwBvADQALAAgAFIATwBBAF8AbwA1ACwAIABDAEYATwBBAF8AbwA1ACwAIABSAE8AQQBfAG8ANgAsACAAQwBGAE8AQQBfAG8ANgAsAFwAbgAgACAAIAAgACgAMQAgACsAIAAoACgAUgBPAEEAXwBvADEAIAAqACAAQwBGAE8AQQBfAG8AMQApACAAKwAgACgAUgBPAEEAXwBvADIAIAAqACAAQwBGAE8AQQBfAG8AMgApACAAKwAgACgAUgBPAEEAXwBvADMAIAAqACAAQwBGAE8AQQBfAG8AMwApACsAIAAoAFIATwBBAF8AbwA0ACAAKgAgAEMARgBPAEEAXwBvADQAKQAgACsAIAAoAFIATwBBAF8AbwA1ACAAKgAgAEMARgBPAEEAXwBvADUAKQAgACsAIAAoAFIATwBBAF8AbwA2ACAAKgAgAEMARgBPAEEAXwBvADYAKQApACkAIABeACAAMAAuADUAOQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMAIABzAGMAYQBsAGkAbgBnACAAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwBGAF8AbwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADcALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMARgBfAG8APQAoADEAKwBcAFwAcwB1AG0AXwBvAFIATwBBAF8AbwBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AKQBeAHsAMAAuADUAOQB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAEYAXwBvAD0AKAAxACsAIAAoACgAUgBPAEEAXwBvADEAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADEAKQAgACsAIAAoAFIATwBBAF8AbwAyAFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwAyACkAIAArACAAKABSAE8AQQBfAG8AMwBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8AMwApACAAKwAgACgAUgBPAEEAXwBvADQAXABcAHQAaQBtAGUAcwAgAEMARgBPAEEAXwBvADQAKQAgACsAIAAoAFIATwBBAF8AbwA1AFwAXAB0AGkAbQBlAHMAIABDAEYATwBBAF8AbwA1ACkAIAArACAAKABSAE8AQQBfAG8ANgBcAFwAdABpAG0AZQBzACAAQwBGAE8AQQBfAG8ANgApACkAXgB7ADAALgA1ADkAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA0ACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIATwBBAF8AbwBcACIALAAgAFwAIgBhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAByAGEAdABlACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAbwBcACIALAAgAFwAIgB0AG8AbgBuAGUAcwAvAGgAYQBcACIALAAgAFwAIgBJAG4AcAB1AHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMARgBPAEEAXwBvAFwAIgAsACAAXAAiAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABhAG0AZQBuAGQAbQBlAG4AdAAgAG8AXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAXAAiAEMAbwBuAHMAdABhAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAbwBcACIALAAgAFwAIgBvAHIAZwBhAG4AaQBjACAAYQBtAGUAbgBkAG0AZQBuAHQAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBwAHUAdABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBjAGwAdQBkAGUAZAAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcwAgAGEAbQBlAG4AZABtAGUAbgB0ACAAYQBzACAAcABlAHIAIABWAEUARQBSAEcAIABlAHEAdQBhAHQAaQBvAG4AIABkAGUAcwBjAHIAaQBwAHQAaQBvAG4AOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAcgBlACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAaQBzACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHQAaABlACAAcgBpAGMAZQAgAGYAaQBlAGwAZABzACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAbwByAGcAYQBuAGkAYwAgAGEAbQBlAG4AZABtAGUAbgB0AHMALAAgAFMARgBfAG8AIABpAHMAIABzAGUAdAAgAHQAbwAgADEALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGMAbABhAHIAZQBkACAAZQBhAGMAaAAgAGEAbQBlAG4AZABtAGUAbgB0ACAAcwBlAHAAYQByAGEAdABlAGwAeQAgAHQAbwAgAGEAbABsAG8AdwAgAHMAdQBtAG0AaQBuAGcAIABpAG4AIABFAHgAYwBlAGwAIABpAG4AIABvAG4AZQAgAGUAcQB1AGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGUAbgBzAGkAdAB5AE8AZgBNAGUAdABoAGEAbgBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABHAGEAcwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEEAcABwAGUAbgBkAGkAYwBlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBHAHIAbwB3AGkAbgBnAFMAZQBhAHMAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIARwByAG8AdwBpAG4AZwBTAGUAYQBzAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAEcAcgBvAHcAaQBuAGcAUwBlAGEAcwBvAG4AXwBEAGEAdABhACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBXAGEAdABlAHIAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBQAHIAZQBTAGUAYQBzAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFcAYQB0AGUAcgBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAFAAcgBlAFMAZQBhAHMAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVwBhAHQAZQByAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAUAByAGUAUwBlAGEAcwBvAG4AXwBEAGEAdABhACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAQwBvAG4AdgBlAHIAcwBpAG8AbgBGAGEAYwB0AG8AcgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABDAG8AbgB2AGUAcgBzAGkAbwBuAEYAYQBjAHQAbwByAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AEMAbwBuAHYAZQByAHMAaQBvAG4ARgBhAGMAdABvAHIAXwBEAGEAdABhACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBUAGkAdABsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBCAGEAcwBlAGwAaQBuAGUARQBGAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQgBhAHMAZQBsAGkAbgBlAEUARgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEIAYQBzAGUAbABpAG4AZQBFAEYAXwBEAGEAdABhACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAxAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADEAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADIAXwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIARgBvAHIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAyAF8ARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAEYAbwByAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMgBfAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBGAG8AcgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AVABpAHQAbABlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFUAbgBpAHQAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFMAbwB1AHIAYwBlACIALAAiAFIAaQBjAGUAQwB1AGwAdABpAHYAYQB0AGkAbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA3AF8AMQBfADEAXwAxAF8AXwAzAF8ATwByAGcAYQBuAGkAYwBBAG0AZQBuAGQAbQBlAG4AdABzAFMAYwBhAGwAaQBuAGcARgBhAGMAdABvAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGkAYwBlAEMAdQBsAHQAaQB2AGEAdABpAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8ANwBfADEAXwAxAF8AMQBfAF8AMwBfAE8AcgBnAGEAbgBpAGMAQQBtAGUAbgBkAG0AZQBuAHQAcwBTAGMAYQBsAGkAbgBnAEYAYQBjAHQAbwByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUgBpAGMAZQBDAHUAbAB0AGkAdgBhAHQAaQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADcAXwAxAF8AMQBfADEAXwBfADMAXwBPAHIAZwBhAG4AaQBjAEEAbQBlAG4AZABtAGUAbgB0AHMAUwBjAGEAbABpAG4AZwBGAGEAYwB0AG8AcgBfAFYAYQByAGkAYQB0AGkAbwBuACIAXQAsACIAbABvAGMAYQBsAGUAIgA6AHsAIgBsAGkAcwB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAcgBvAHcAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBjAG8AbAB1AG0AbgBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUABvAHMAaQB0AGkAbwBuAHMAIgA6AFsAMwBdACwAIgBkAGUAYwBpAG0AYQBsAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiAC4AIgAsACIAZABhAHQAZQBPAHIAZABlAHIAIgA6ACIARABNAFkAIgAsACIAYwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsACIAOgAiACQAIgAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbABMAGUAYQBkACIAOgB0AHIAdQBlACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAZQBwAEIAeQBTAHAAYQBjAGUAIgA6AGYAYQBsAHMAZQAsACIAcgBvAHcATABlAHQAdABlAHIAIgA6ACIAUgAiACwAIgBjAG8AbAB1AG0AbgBMAGUAdAB0AGUAcgAiADoAIgBDACIALAAiAHIAYwBMAGUAZgB0AEIAcgBhAGMAawBlAHQAIgA6ACIAWwAiACwAIgByAGMAUgBpAGcAaAB0AEIAcgBhAGMAawBlAHQAIgA6ACIAXQAiACwAIgBzAHQAYQB0AGUAbQBlAG4AdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGwAbwBjAGEAbABlAE4AYQBtAGUAIgA6ACIAZQBuAC0AdQBzACIAfQB9AA==</AFEJSONBlob>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -16909,12 +16961,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Excel/7_RiceCultivation_WIP_v01.xlsx
+++ b/Excel/7_RiceCultivation_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E701DC-2B92-4BA7-9D96-DD372C51324D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE636FF0-E379-4CAF-9430-9D783A9C6F33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" firstSheet="3" activeTab="7" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="825" yWindow="345" windowWidth="37335" windowHeight="19740" firstSheet="3" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -22,9 +22,6 @@
     <sheet name="Constants - Rice cultivation" sheetId="110" r:id="rId7"/>
     <sheet name="Constants - Common" sheetId="119" r:id="rId8"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId9"/>
-  </externalReferences>
   <definedNames>
     <definedName name="AgResidues_Equations_Leaching.VEERG_6_3_1_1__1__LeachingAndRunoffEmissionsCropAndPastureResidue">_xlfn.LAMBDA(_xlpm.Mleachcp,_xlpm.EFleach,_xlpm.CgN2O, _xlpm.Mleachcp * _xlpm.EFleach * _xlpm.CgN2O * 10 ^ (-3))</definedName>
     <definedName name="AgResidues_Equations_Leaching.VEERG_6_3_1_1__1__LeachingAndRunoffEmissionsCropAndPastureResidue_Arguments">_xlfn.LAMBDA(_xlfn.MAKEARRAY(5, 2, _xlfn.LAMBDA(_xlpm.r,_xlpm.c, INDEX({"Mleachcp","mass of nitrogen lost through leaching and runoff from the crop residue c or pasture residue p (kg N)";"EFleach","emission factor for leaching and runoff (kg N2O-N/kg N)";"CgN2O","factor to convert elemental mass of nitrous oxide to molecular mass (dimensionless)";"c","Crop residue type";"p","Pasture residue type"}, _xlpm.r, _xlpm.c))))</definedName>
@@ -1928,7 +1925,7 @@
     </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="40" fillId="4" borderId="0" xfId="8">
       <alignment horizontal="left" vertical="center"/>
@@ -2263,9 +2260,6 @@
     <xf numFmtId="0" fontId="22" fillId="10" borderId="0" xfId="37">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="13" borderId="0" xfId="41" applyBorder="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="70">
     <cellStyle name="Alert" xfId="62" xr:uid="{34EFE908-8095-4010-8F93-8CFE88055637}"/>
@@ -2340,6 +2334,126 @@
     <cellStyle name="Variable type other" xfId="66" xr:uid="{6646F6F7-E4F9-4165-8015-E25083532B5B}"/>
   </cellStyles>
   <dxfs count="66">
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC44340"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3201,126 +3315,6 @@
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC44340"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7012,26 +7006,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Home"/>
-      <sheetName val="Constants - Common"/>
-      <sheetName val="Acknowledgements"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -7110,7 +7084,7 @@
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{FE260FFD-8165-44FA-8171-CF7DA9E6EDC2}" name="Amendment mix name"/>
     <tableColumn id="2" xr3:uid="{1656D970-5568-46C3-8CF9-6544B58E60EE}" name="Straw added &lt; 30 days before cultivation (t/ha)"/>
-    <tableColumn id="8" xr3:uid="{6AB8226E-B5ED-4236-BF1D-312497BC4C8F}" name="Straw added 30+ days before cultivation (t/ha)" dataDxfId="53" dataCellStyle="Content normal"/>
+    <tableColumn id="8" xr3:uid="{6AB8226E-B5ED-4236-BF1D-312497BC4C8F}" name="Straw added 30+ days before cultivation (t/ha)" dataDxfId="17" dataCellStyle="Content normal"/>
     <tableColumn id="3" xr3:uid="{7414D722-C23C-43BF-8BE4-9A787F770773}" name="Compost (t/ha)"/>
     <tableColumn id="4" xr3:uid="{10821F0A-FFAB-47C5-A2D8-0C77A91D1E11}" name="Farm yard manure (t/ha)"/>
     <tableColumn id="5" xr3:uid="{7554AF1F-8437-4EC1-A35B-D5ADAFFC9535}" name="Green manure (t/ha)"/>
@@ -7206,49 +7180,49 @@
     <tableColumn id="1" xr3:uid="{E3EAE8D7-79F7-4CFF-AA60-81BEB0D1F996}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{90558006-D3B7-45CA-BB08-CBC5FB2D525E}" name="MAT" totalsRowDxfId="35" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{90558006-D3B7-45CA-BB08-CBC5FB2D525E}" name="MAT" totalsRowDxfId="53" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{31536C54-9D90-4BA1-8630-5A5825932E3D}" name="MAP" totalsRowDxfId="34" totalsRowCellStyle="Content bold">
+    <tableColumn id="3" xr3:uid="{31536C54-9D90-4BA1-8630-5A5825932E3D}" name="MAP" totalsRowDxfId="52" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C736DFB1-216D-41C0-9BDA-AF1DACA0D28E}" name="Frost days per year" totalsRowDxfId="33" totalsRowCellStyle="Content bold">
+    <tableColumn id="4" xr3:uid="{C736DFB1-216D-41C0-9BDA-AF1DACA0D28E}" name="Frost days per year" totalsRowDxfId="51" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{EBC9733B-D9D6-44EF-92E6-EAE63368707E}" name="Elevation" totalsRowDxfId="32" totalsRowCellStyle="Content bold">
+    <tableColumn id="5" xr3:uid="{EBC9733B-D9D6-44EF-92E6-EAE63368707E}" name="Elevation" totalsRowDxfId="50" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{86BD24B4-BCF5-43E4-9791-66486A239A29}" name="MAP:PET" totalsRowDxfId="31" totalsRowCellStyle="Content bold">
+    <tableColumn id="6" xr3:uid="{86BD24B4-BCF5-43E4-9791-66486A239A29}" name="MAP:PET" totalsRowDxfId="49" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{04625927-EE66-47A4-9B56-E9FF16A40381}" name="Min temp" totalsRowDxfId="30" totalsRowCellStyle="Content bold">
+    <tableColumn id="7" xr3:uid="{04625927-EE66-47A4-9B56-E9FF16A40381}" name="Min temp" totalsRowDxfId="48" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{0B6D7849-AF37-4F92-B3BC-F00F938473A4}" name="Max temp" totalsRowDxfId="29" totalsRowCellStyle="Content bold">
+    <tableColumn id="8" xr3:uid="{0B6D7849-AF37-4F92-B3BC-F00F938473A4}" name="Max temp" totalsRowDxfId="47" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{79B2D447-365C-4E5B-9B46-EB9A6FEABC8F}" name="Min rainfall" totalsRowDxfId="28" totalsRowCellStyle="Content bold">
+    <tableColumn id="9" xr3:uid="{79B2D447-365C-4E5B-9B46-EB9A6FEABC8F}" name="Min rainfall" totalsRowDxfId="46" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{15AE00CB-0DCC-4C76-9A69-811B2102ABD0}" name="Max rainfall" totalsRowDxfId="27" totalsRowCellStyle="Content bold">
+    <tableColumn id="10" xr3:uid="{15AE00CB-0DCC-4C76-9A69-811B2102ABD0}" name="Max rainfall" totalsRowDxfId="45" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{453B192C-DCF9-4759-9B4F-A3C3978C4EAF}" name="Min frost days" totalsRowDxfId="26" totalsRowCellStyle="Content bold">
+    <tableColumn id="11" xr3:uid="{453B192C-DCF9-4759-9B4F-A3C3978C4EAF}" name="Min frost days" totalsRowDxfId="44" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{399D591D-E030-4FE8-8A4D-14B154F55401}" name="Max frost days" totalsRowDxfId="25" totalsRowCellStyle="Content bold">
+    <tableColumn id="15" xr3:uid="{399D591D-E030-4FE8-8A4D-14B154F55401}" name="Max frost days" totalsRowDxfId="43" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{7BB2477B-60BA-4ACB-81E8-FD8FE87495FF}" name="Min elevation" totalsRowDxfId="24" totalsRowCellStyle="Content bold">
+    <tableColumn id="12" xr3:uid="{7BB2477B-60BA-4ACB-81E8-FD8FE87495FF}" name="Min elevation" totalsRowDxfId="42" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{0A47AD04-56FF-4DD7-A870-3813EAA5B320}" name="Max elevation" totalsRowDxfId="23" totalsRowCellStyle="Content bold">
+    <tableColumn id="16" xr3:uid="{0A47AD04-56FF-4DD7-A870-3813EAA5B320}" name="Max elevation" totalsRowDxfId="41" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{FE9A6C0E-201D-4A67-8D4D-C6A488CA05EA}" name="Min MAP:PET" totalsRowDxfId="22" totalsRowCellStyle="Content bold">
+    <tableColumn id="13" xr3:uid="{FE9A6C0E-201D-4A67-8D4D-C6A488CA05EA}" name="Min MAP:PET" totalsRowDxfId="40" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{3378CC43-2399-435F-A3FE-BB19D039E80F}" name="Max MAP:PET" totalsRowDxfId="21" totalsRowCellStyle="Content bold">
+    <tableColumn id="17" xr3:uid="{3378CC43-2399-435F-A3FE-BB19D039E80F}" name="Max MAP:PET" totalsRowDxfId="39" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7266,7 +7240,7 @@
     <tableColumn id="1" xr3:uid="{1ECE3957-9413-4408-BDB8-77552A7231E8}" name="Climate zone" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{03FFA737-2FA7-48E9-A115-73FA50C9393D}" name="Wet or Dry Zone" totalsRowDxfId="20" totalsRowCellStyle="Content bold">
+    <tableColumn id="2" xr3:uid="{03FFA737-2FA7-48E9-A115-73FA50C9393D}" name="Wet or Dry Zone" totalsRowDxfId="38" totalsRowCellStyle="Content bold">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7372,7 +7346,7 @@
     <tableColumn id="1" xr3:uid="{1FF542F2-F612-45D7-AC03-2F170C811D2C}" name="Is in leaching zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{CAF3234F-1744-4CC7-97FB-29E26283D105}" name="FracWET" dataDxfId="19">
+    <tableColumn id="2" xr3:uid="{CAF3234F-1744-4CC7-97FB-29E26283D105}" name="FracWET" dataDxfId="37">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7393,7 +7367,7 @@
   </autoFilter>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{6CF21226-E2F8-4356-887C-701D50A69505}" name="Regime name"/>
-    <tableColumn id="7" xr3:uid="{03F35653-B2DB-4AB6-99EC-0912FB20CD21}" name="Area under cultivation (hectares)" dataDxfId="52" dataCellStyle="Content normal"/>
+    <tableColumn id="7" xr3:uid="{03F35653-B2DB-4AB6-99EC-0912FB20CD21}" name="Area under cultivation (hectares)" dataDxfId="16" dataCellStyle="Content normal"/>
     <tableColumn id="2" xr3:uid="{EA5A5A10-60BF-4C8A-8D3B-469871BE7F8E}" name="Pre-cultivation water regime (select)" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{85A41168-485F-4954-954D-E24F2E46EB1B}" name="Water regime (select)" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{EF7FE10B-862C-4478-9622-5C7E7DA42BCC}" name="Water regime sub-type (select)" dataCellStyle="Input select"/>
@@ -7444,7 +7418,7 @@
     <tableColumn id="1" xr3:uid="{0349773D-F8B1-4F20-8D67-02CFFC1D5B01}" name="Irrigation type i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E1A81332-451C-4F13-819A-08B47B324E1A}" name="FracWET" dataDxfId="18" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{E1A81332-451C-4F13-819A-08B47B324E1A}" name="FracWET" dataDxfId="36" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7462,7 +7436,7 @@
     <tableColumn id="1" xr3:uid="{19ECEEA9-A0E2-448E-9242-5EB4612E5A30}" name="Climate zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D5BC812F-1B20-433B-A220-45B290E585E4}" name="EFPRP" dataDxfId="17" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{D5BC812F-1B20-433B-A220-45B290E585E4}" name="EFPRP" dataDxfId="35" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7480,7 +7454,7 @@
     <tableColumn id="1" xr3:uid="{622EF0B5-08C2-435D-AD90-194AA40AF483}" name="Month">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1B155342-2AE7-4ACF-A9BA-20CE30CBC6E1}" name="Season" dataDxfId="16" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1B155342-2AE7-4ACF-A9BA-20CE30CBC6E1}" name="Season" dataDxfId="34" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7512,49 +7486,49 @@
     <tableColumn id="1" xr3:uid="{3E609039-97C4-4729-BC48-B95334FF569D}" name="Temperature zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E18B5A5E-83DE-4F01-B188-8A16EF097844}" name="MAT (ºC)" dataDxfId="15" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{E18B5A5E-83DE-4F01-B188-8A16EF097844}" name="MAT (ºC)" dataDxfId="33" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{D36388A3-2885-4653-8CA5-464AC2653131}" name="Anaerobic lagoon" dataDxfId="14" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{D36388A3-2885-4653-8CA5-464AC2653131}" name="Anaerobic lagoon" dataDxfId="32" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{9C1AA35B-D1B9-4F13-9AFE-E084527288D4}" name="Digester / covered lagoons" dataDxfId="13" dataCellStyle="Content normal">
+    <tableColumn id="4" xr3:uid="{9C1AA35B-D1B9-4F13-9AFE-E084527288D4}" name="Digester / covered lagoons" dataDxfId="31" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{36AFD6DE-B5F7-4FA0-8661-5137CBBDF314}" name="Liquid systems" dataDxfId="12" dataCellStyle="Content normal">
+    <tableColumn id="5" xr3:uid="{36AFD6DE-B5F7-4FA0-8661-5137CBBDF314}" name="Liquid systems" dataDxfId="30" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{5C9AC720-CEA6-4B40-B794-DA1221D8A639}" name="Daily spread" dataDxfId="11" dataCellStyle="Content normal">
+    <tableColumn id="6" xr3:uid="{5C9AC720-CEA6-4B40-B794-DA1221D8A639}" name="Daily spread" dataDxfId="29" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{454AD809-4295-4C51-9928-79A9335C5131}" name="Composting (passive windrow)" dataDxfId="10" dataCellStyle="Content normal">
+    <tableColumn id="7" xr3:uid="{454AD809-4295-4C51-9928-79A9335C5131}" name="Composting (passive windrow)" dataDxfId="28" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{3B58D073-0610-4780-89E8-72FD5F9DE29F}" name="Solid storage" dataDxfId="9" dataCellStyle="Content normal">
+    <tableColumn id="8" xr3:uid="{3B58D073-0610-4780-89E8-72FD5F9DE29F}" name="Solid storage" dataDxfId="27" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{4054B9BB-77F9-4163-856D-1F02090BD29E}" name="Pit storage" dataDxfId="8" dataCellStyle="Content normal">
+    <tableColumn id="9" xr3:uid="{4054B9BB-77F9-4163-856D-1F02090BD29E}" name="Pit storage" dataDxfId="26" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{7761C4A1-7DEB-4A74-ABFE-16C4A40CA65E}" name="Deep litter" dataDxfId="7" dataCellStyle="Content normal">
+    <tableColumn id="10" xr3:uid="{7761C4A1-7DEB-4A74-ABFE-16C4A40CA65E}" name="Deep litter" dataDxfId="25" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{8CBEF1D1-4341-4566-AE85-0BAE80513B23}" name="Poultry manure with bedding" dataDxfId="6" dataCellStyle="Content normal">
+    <tableColumn id="11" xr3:uid="{8CBEF1D1-4341-4566-AE85-0BAE80513B23}" name="Poultry manure with bedding" dataDxfId="24" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{8AC3B56F-0E3B-46E4-881E-4A4C23336DB8}" name="Poultry manure without bedding" dataDxfId="5" dataCellStyle="Content normal">
+    <tableColumn id="12" xr3:uid="{8AC3B56F-0E3B-46E4-881E-4A4C23336DB8}" name="Poultry manure without bedding" dataDxfId="23" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{5E2D555B-CCCB-47A0-ABC6-4BBE59B69EB8}" name="Direct processing" dataDxfId="4" dataCellStyle="Content normal">
+    <tableColumn id="13" xr3:uid="{5E2D555B-CCCB-47A0-ABC6-4BBE59B69EB8}" name="Direct processing" dataDxfId="22" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{1ABF9296-D829-4357-B8D0-BF198B1CB558}" name="Direct application" dataDxfId="3" dataCellStyle="Content normal">
+    <tableColumn id="14" xr3:uid="{1ABF9296-D829-4357-B8D0-BF198B1CB558}" name="Direct application" dataDxfId="21" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{143C946F-C17F-411D-99BA-FB5337573E30}" name="Pasture range and paddock" dataDxfId="2" dataCellStyle="Content normal">
+    <tableColumn id="15" xr3:uid="{143C946F-C17F-411D-99BA-FB5337573E30}" name="Pasture range and paddock" dataDxfId="20" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{6876FAEC-5772-4EAC-8F56-60AF713901CD}" name="MAT raw" dataDxfId="1" dataCellStyle="Content normal">
+    <tableColumn id="16" xr3:uid="{6876FAEC-5772-4EAC-8F56-60AF713901CD}" name="MAT raw" dataDxfId="19" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7572,7 +7546,7 @@
     <tableColumn id="1" xr3:uid="{9C964A67-F781-4D99-8B91-5BFC8B5214FC}" name="Climate Zone">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EC008960-0F7E-4D6F-90B0-1B33D47696C5}" name="EFNi &amp; EFN2Oi" dataDxfId="0" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{EC008960-0F7E-4D6F-90B0-1B33D47696C5}" name="EFNi &amp; EFN2Oi" dataDxfId="18" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7591,10 +7565,10 @@
     <tableColumn id="1" xr3:uid="{3A2980B6-3A2D-485C-8340-4AB52CBFBB99}" name="Water regime type">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorGrowingSeason_Data(),Table_SourceData_WaterScalingFactorGrowingSeason[[#Headers],[Water regime type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{49BAF191-8DE2-478B-90F3-B9943FCEA9BA}" name="Water regime sub-type" dataDxfId="51" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{49BAF191-8DE2-478B-90F3-B9943FCEA9BA}" name="Water regime sub-type" dataDxfId="15" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorGrowingSeason_Data(),Table_SourceData_WaterScalingFactorGrowingSeason[[#Headers],[Water regime type]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{5202109C-BFD9-4463-9F2B-0B19C4500C07}" name="SFw" dataDxfId="50" dataCellStyle="Content normal">
+    <tableColumn id="3" xr3:uid="{5202109C-BFD9-4463-9F2B-0B19C4500C07}" name="SFw" dataDxfId="14" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorGrowingSeason_Data(),Table_SourceData_WaterScalingFactorGrowingSeason[[#Headers],[Water regime type]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7612,7 +7586,7 @@
     <tableColumn id="1" xr3:uid="{FF0717D8-C262-491B-A316-62679EA1B7D7}" name="Water regime prior to cultivation">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Data(),Table_SourceData_WaterScalingFactorPreSeason[[#Headers],[Water regime prior to cultivation]], 0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3527B004-E130-4F0F-B6D1-0D475D57A7A4}" name="SFp" dataDxfId="49" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{3527B004-E130-4F0F-B6D1-0D475D57A7A4}" name="SFp" dataDxfId="13" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_WaterScalingFactorPreSeason_Data(),Table_SourceData_WaterScalingFactorPreSeason[[#Headers],[Water regime prior to cultivation]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7630,7 +7604,7 @@
     <tableColumn id="1" xr3:uid="{4FCCD68A-6FAE-4D17-88E1-28AE833F5E5E}" name="Organic amendment i">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Data(),Table15[[#Headers],[Organic amendment i]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1F56CED6-01B8-4B36-AC56-E8A59F878F68}" name="CFOAi" dataDxfId="48" dataCellStyle="Content normal">
+    <tableColumn id="2" xr3:uid="{1F56CED6-01B8-4B36-AC56-E8A59F878F68}" name="CFOAi" dataDxfId="12" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(RiceCultivation_SourceData.SourceData_RiceCultivation_OrganicAmendmentConversionFactor_Data(),Table15[[#Headers],[Organic amendment i]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10152,9 +10126,6 @@
       <c r="E7" s="83"/>
       <c r="F7" s="83"/>
       <c r="G7" s="78"/>
-      <c r="H7" s="122"/>
-      <c r="I7" s="122"/>
-      <c r="J7" s="122"/>
     </row>
     <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="str">
@@ -10547,62 +10518,62 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F86">
-    <cfRule type="cellIs" dxfId="47" priority="62" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="62" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F128:F129">
-    <cfRule type="cellIs" dxfId="46" priority="21" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="21" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F140:F141">
-    <cfRule type="cellIs" dxfId="45" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="20" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F152:F153">
-    <cfRule type="cellIs" dxfId="44" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="19" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F164:F165">
-    <cfRule type="cellIs" dxfId="43" priority="18" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F252:F253">
-    <cfRule type="cellIs" dxfId="42" priority="93" operator="lessThan">
+    <cfRule type="cellIs" dxfId="6" priority="93" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F257:F258">
-    <cfRule type="cellIs" dxfId="41" priority="92" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="92" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F262:F263">
-    <cfRule type="cellIs" dxfId="40" priority="91" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="91" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F286:F287">
-    <cfRule type="cellIs" dxfId="39" priority="85" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="85" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F291:F292">
-    <cfRule type="cellIs" dxfId="38" priority="84" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="84" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F296:F297">
-    <cfRule type="cellIs" dxfId="37" priority="83" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="83" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J211 E212:I212">
-    <cfRule type="cellIs" dxfId="36" priority="79" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="79" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16712,14 +16683,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16918,12 +16887,14 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16931,12 +16902,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -16961,9 +16929,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
